--- a/RNR_수입원가_2026_20260506.xlsx
+++ b/RNR_수입원가_2026_20260506.xlsx
@@ -2058,16 +2058,8 @@
           <t>Parts (국내)</t>
         </is>
       </c>
-      <c r="O8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O8" s="12" t="n"/>
+      <c r="P8" s="12" t="n"/>
       <c r="Q8" s="18" t="n"/>
       <c r="R8" s="18" t="n"/>
       <c r="S8" s="18" t="n">
@@ -2110,11 +2102,7 @@
         <f>ROUND(AA8/AB8,0)</f>
         <v/>
       </c>
-      <c r="AD8" s="12" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
+      <c r="AD8" s="12" t="n"/>
       <c r="AE8" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3876,16 +3864,8 @@
           <t>Projector (한국)</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P22" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O22" s="12" t="n"/>
+      <c r="P22" s="12" t="n"/>
       <c r="Q22" s="18" t="n"/>
       <c r="R22" s="18" t="n"/>
       <c r="S22" s="18" t="n">
@@ -3928,11 +3908,7 @@
         <f>ROUND(AA22/AB22,0)</f>
         <v/>
       </c>
-      <c r="AD22" s="12" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
+      <c r="AD22" s="12" t="n"/>
       <c r="AE22" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5015,16 +4991,8 @@
           <t>AXC 200 ELICENT 60ea (EUR / 재고)</t>
         </is>
       </c>
-      <c r="O31" s="149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P31" s="78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O31" s="149" t="n"/>
+      <c r="P31" s="78" t="n"/>
       <c r="Q31" s="151">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5069,11 +5037,7 @@
       <c r="AC31" s="83" t="n">
         <v>129393</v>
       </c>
-      <c r="AD31" s="78" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
+      <c r="AD31" s="78" t="n"/>
       <c r="AE31" s="78" t="n"/>
       <c r="AF31" s="78" t="n"/>
     </row>
@@ -5134,16 +5098,8 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="O32" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P32" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O32" s="20" t="n"/>
+      <c r="P32" s="20" t="n"/>
       <c r="Q32" s="26">
         <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5265,16 +5221,8 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="O33" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P33" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O33" s="20" t="n"/>
+      <c r="P33" s="20" t="n"/>
       <c r="Q33" s="26">
         <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5396,16 +5344,8 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="O34" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P34" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O34" s="20" t="n"/>
+      <c r="P34" s="20" t="n"/>
       <c r="Q34" s="26">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5527,16 +5467,8 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="O35" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P35" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O35" s="20" t="n"/>
+      <c r="P35" s="20" t="n"/>
       <c r="Q35" s="26">
         <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5658,16 +5590,8 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="O36" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P36" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O36" s="20" t="n"/>
+      <c r="P36" s="20" t="n"/>
       <c r="Q36" s="26">
         <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5789,16 +5713,8 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="O37" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P37" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O37" s="20" t="n"/>
+      <c r="P37" s="20" t="n"/>
       <c r="Q37" s="26">
         <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5922,16 +5838,8 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="O38" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P38" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O38" s="20" t="n"/>
+      <c r="P38" s="20" t="n"/>
       <c r="Q38" s="26">
         <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6053,16 +5961,8 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="O39" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P39" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O39" s="20" t="n"/>
+      <c r="P39" s="20" t="n"/>
       <c r="Q39" s="26">
         <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6186,16 +6086,8 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="O40" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P40" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O40" s="20" t="n"/>
+      <c r="P40" s="20" t="n"/>
       <c r="Q40" s="26">
         <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6317,16 +6209,8 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="O41" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P41" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O41" s="20" t="n"/>
+      <c r="P41" s="20" t="n"/>
       <c r="Q41" s="26">
         <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6448,16 +6332,8 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="O42" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P42" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O42" s="20" t="n"/>
+      <c r="P42" s="20" t="n"/>
       <c r="Q42" s="26">
         <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6579,16 +6455,8 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="O43" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P43" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O43" s="20" t="n"/>
+      <c r="P43" s="20" t="n"/>
       <c r="Q43" s="26">
         <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6710,16 +6578,8 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="O44" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P44" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O44" s="20" t="n"/>
+      <c r="P44" s="20" t="n"/>
       <c r="Q44" s="26">
         <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6841,16 +6701,8 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="O45" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P45" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O45" s="20" t="n"/>
+      <c r="P45" s="20" t="n"/>
       <c r="Q45" s="26">
         <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6972,16 +6824,8 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="O46" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P46" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O46" s="20" t="n"/>
+      <c r="P46" s="20" t="n"/>
       <c r="Q46" s="26">
         <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7103,16 +6947,8 @@
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="O47" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P47" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O47" s="20" t="n"/>
+      <c r="P47" s="20" t="n"/>
       <c r="Q47" s="26">
         <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7234,16 +7070,8 @@
           <t>EW (CGV 동백 외)</t>
         </is>
       </c>
-      <c r="O48" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P48" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O48" s="20" t="n"/>
+      <c r="P48" s="20" t="n"/>
       <c r="Q48" s="26">
         <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7367,16 +7195,8 @@
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O49" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O49" s="155" t="n"/>
+      <c r="P49" s="85" t="n"/>
       <c r="Q49" s="157">
         <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7490,16 +7310,8 @@
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O50" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P50" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O50" s="155" t="n"/>
+      <c r="P50" s="85" t="n"/>
       <c r="Q50" s="157">
         <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7613,16 +7425,8 @@
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P51" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="O51" s="12" t="n"/>
+      <c r="P51" s="12" t="n"/>
       <c r="Q51" s="18">
         <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE()),""))</f>
         <v/>

--- a/RNR_수입원가_2026_20260506.xlsx
+++ b/RNR_수입원가_2026_20260506.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="환율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="FxRateTable">환율!$A$7:$D$34</definedName>
     <definedName name="RemitTable1">외화송금내역!$A$3:$L$34</definedName>
     <definedName name="RemitTable2">외화송금내역!$A$37:$L$74</definedName>
+    <definedName name="FxRateTable">환율!$A$7:$D$37</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16096,7 +16096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="15" customWidth="1" style="40" min="1" max="2"/>
@@ -16631,6 +16631,38 @@
       </c>
       <c r="D35" s="7" t="n">
         <v>1479.34</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="144" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B36" s="144" t="n">
+        <v>46144</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1476.92</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="144" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B37" s="144" t="n">
+        <v>46151</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1476.35</v>
       </c>
     </row>
   </sheetData>

--- a/RNR_수입원가_2026_20260506.xlsx
+++ b/RNR_수입원가_2026_20260506.xlsx
@@ -5098,8 +5098,16 @@
           <t>EW CP2220</t>
         </is>
       </c>
-      <c r="O32" s="20" t="n"/>
-      <c r="P32" s="20" t="n"/>
+      <c r="O32" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q32" s="26">
         <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5221,8 +5229,16 @@
           <t>HFR License</t>
         </is>
       </c>
-      <c r="O33" s="20" t="n"/>
-      <c r="P33" s="20" t="n"/>
+      <c r="O33" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q33" s="26">
         <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5344,8 +5360,16 @@
           <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
-      <c r="O34" s="20" t="n"/>
-      <c r="P34" s="20" t="n"/>
+      <c r="O34" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q34" s="26">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5467,8 +5491,16 @@
           <t>TMS-2000 EW</t>
         </is>
       </c>
-      <c r="O35" s="20" t="n"/>
-      <c r="P35" s="20" t="n"/>
+      <c r="O35" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P35" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q35" s="26">
         <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5590,8 +5622,16 @@
           <t>TMS-1000 EW</t>
         </is>
       </c>
-      <c r="O36" s="20" t="n"/>
-      <c r="P36" s="20" t="n"/>
+      <c r="O36" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P36" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q36" s="26">
         <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5713,8 +5753,16 @@
           <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
-      <c r="O37" s="20" t="n"/>
-      <c r="P37" s="20" t="n"/>
+      <c r="O37" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P37" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q37" s="26">
         <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5838,8 +5886,16 @@
           <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
-      <c r="O38" s="20" t="n"/>
-      <c r="P38" s="20" t="n"/>
+      <c r="O38" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P38" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q38" s="26">
         <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -5961,8 +6017,16 @@
           <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
-      <c r="O39" s="20" t="n"/>
-      <c r="P39" s="20" t="n"/>
+      <c r="O39" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P39" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q39" s="26">
         <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6086,8 +6150,16 @@
           <t>EW (홀딩)</t>
         </is>
       </c>
-      <c r="O40" s="20" t="n"/>
-      <c r="P40" s="20" t="n"/>
+      <c r="O40" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P40" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q40" s="26">
         <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6209,8 +6281,16 @@
           <t>TMS-2000 License</t>
         </is>
       </c>
-      <c r="O41" s="20" t="n"/>
-      <c r="P41" s="20" t="n"/>
+      <c r="O41" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q41" s="26">
         <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6332,8 +6412,16 @@
           <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
-      <c r="O42" s="20" t="n"/>
-      <c r="P42" s="20" t="n"/>
+      <c r="O42" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P42" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q42" s="26">
         <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6455,8 +6543,16 @@
           <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
-      <c r="O43" s="20" t="n"/>
-      <c r="P43" s="20" t="n"/>
+      <c r="O43" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P43" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q43" s="26">
         <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6578,8 +6674,16 @@
           <t>EW (메가박스 외)</t>
         </is>
       </c>
-      <c r="O44" s="20" t="n"/>
-      <c r="P44" s="20" t="n"/>
+      <c r="O44" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P44" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q44" s="26">
         <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6701,8 +6805,16 @@
           <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
-      <c r="O45" s="20" t="n"/>
-      <c r="P45" s="20" t="n"/>
+      <c r="O45" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P45" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q45" s="26">
         <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6824,8 +6936,16 @@
           <t>TMS-1000 License</t>
         </is>
       </c>
-      <c r="O46" s="20" t="n"/>
-      <c r="P46" s="20" t="n"/>
+      <c r="O46" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P46" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q46" s="26">
         <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -6947,8 +7067,16 @@
           <t>Dolby Atmos License</t>
         </is>
       </c>
-      <c r="O47" s="20" t="n"/>
-      <c r="P47" s="20" t="n"/>
+      <c r="O47" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P47" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q47" s="26">
         <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7070,8 +7198,16 @@
           <t>EW (CGV 동백 외)</t>
         </is>
       </c>
-      <c r="O48" s="20" t="n"/>
-      <c r="P48" s="20" t="n"/>
+      <c r="O48" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P48" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q48" s="26">
         <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7195,8 +7331,16 @@
           <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
-      <c r="O49" s="155" t="n"/>
-      <c r="P49" s="85" t="n"/>
+      <c r="O49" s="155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q49" s="157">
         <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7310,8 +7454,16 @@
           <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
         </is>
       </c>
-      <c r="O50" s="155" t="n"/>
-      <c r="P50" s="85" t="n"/>
+      <c r="O50" s="155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P50" s="85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q50" s="157">
         <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE()),""))</f>
         <v/>
@@ -7425,8 +7577,16 @@
           <t>Inspection fee</t>
         </is>
       </c>
-      <c r="O51" s="12" t="n"/>
-      <c r="P51" s="12" t="n"/>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Q51" s="18">
         <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE()),""))</f>
         <v/>

--- a/RNR_수입원가_2026_20260506.xlsx
+++ b/RNR_수입원가_2026_20260506.xlsx
@@ -4949,12 +4949,12 @@
       </c>
       <c r="C31" s="78" t="inlineStr">
         <is>
-          <t>Elicent</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D31" s="78" t="inlineStr">
         <is>
-          <t>T/T (EUR)</t>
+          <t>100% TT in advance</t>
         </is>
       </c>
       <c r="E31" s="78" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="N31" s="78" t="inlineStr">
         <is>
-          <t>AXC 200 ELICENT 60ea (EUR / 재고)</t>
+          <t>AXC 200 ELICENT VENTILATORE/FAN (60EA, EUR)</t>
         </is>
       </c>
       <c r="O31" s="149" t="n"/>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="C32" s="103" t="inlineStr">
         <is>
-          <t>Elicent (EUR)</t>
+          <t>MAICO Italia (EUR)</t>
         </is>
       </c>
       <c r="D32" s="102" t="inlineStr">
@@ -14002,7 +14002,7 @@
       </c>
       <c r="C70" s="103" t="inlineStr">
         <is>
-          <t>Elicent</t>
+          <t>MAICO Italia</t>
         </is>
       </c>
       <c r="D70" s="104" t="n">

--- a/RNR_수입원가_2026_20260506.xlsx
+++ b/RNR_수입원가_2026_20260506.xlsx
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="Q5" s="7">
-        <f>IF(P5="","",IFERROR(VLOOKUP(O5,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P5="","",IFERROR(VLOOKUP(O5,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R5" s="7">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="Q6" s="7">
-        <f>IF(P6="","",IFERROR(VLOOKUP(O6,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P6="","",IFERROR(VLOOKUP(O6,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R6" s="7">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="Q7" s="7">
-        <f>IF(P7="","",IFERROR(VLOOKUP(O7,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P7="","",IFERROR(VLOOKUP(O7,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R7" s="7">
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="Q9" s="7">
-        <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R9" s="7">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="Q10" s="7">
-        <f>IF(P10="","",IFERROR(VLOOKUP(O10,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P10="","",IFERROR(VLOOKUP(O10,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R10" s="7">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="Q11" s="7">
-        <f>IF(P11="","",IFERROR(VLOOKUP(O11,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P11="","",IFERROR(VLOOKUP(O11,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R11" s="7">
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="Q12" s="7">
-        <f>IF(P12="","",IFERROR(VLOOKUP(O12,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P12="","",IFERROR(VLOOKUP(O12,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R12" s="7">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="Q13" s="7">
-        <f>IF(P13="","",IFERROR(VLOOKUP(O13,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P13="","",IFERROR(VLOOKUP(O13,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R13" s="7">
@@ -2835,7 +2835,7 @@
         </is>
       </c>
       <c r="Q14" s="7">
-        <f>IF(P14="","",IFERROR(VLOOKUP(O14,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P14="","",IFERROR(VLOOKUP(O14,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R14" s="7">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="Q15" s="7">
-        <f>IF(P15="","",IFERROR(VLOOKUP(O15,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P15="","",IFERROR(VLOOKUP(O15,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R15" s="7">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="Q16" s="7">
-        <f>IF(P16="","",IFERROR(VLOOKUP(O16,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P16="","",IFERROR(VLOOKUP(O16,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R16" s="7">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="Q17" s="7">
-        <f>IF(P17="","",IFERROR(VLOOKUP(O17,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P17="","",IFERROR(VLOOKUP(O17,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R17" s="7">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="Q18" s="7">
-        <f>IF(P18="","",IFERROR(VLOOKUP(O18,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P18="","",IFERROR(VLOOKUP(O18,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R18" s="7">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="Q19" s="7">
-        <f>IF(P19="","",IFERROR(VLOOKUP(O19,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P19="","",IFERROR(VLOOKUP(O19,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R19" s="7">
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="Q20" s="7">
-        <f>IF(P20="","",IFERROR(VLOOKUP(O20,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P20="","",IFERROR(VLOOKUP(O20,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R20" s="7">
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Q21" s="7">
-        <f>IF(P21="","",IFERROR(VLOOKUP(O21,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P21="","",IFERROR(VLOOKUP(O21,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R21" s="7">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="Q23" s="7">
-        <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R23" s="7">
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="Q24" s="7">
-        <f>IF(P24="","",IFERROR(VLOOKUP(O24,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P24="","",IFERROR(VLOOKUP(O24,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R24" s="7">
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="Q25" s="7">
-        <f>IF(P25="","",IFERROR(VLOOKUP(O25,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P25="","",IFERROR(VLOOKUP(O25,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R25" s="7">
@@ -4385,7 +4385,7 @@
         </is>
       </c>
       <c r="Q26" s="7">
-        <f>IF(P26="","",IFERROR(VLOOKUP(O26,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P26="","",IFERROR(VLOOKUP(O26,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R26" s="7">
@@ -4516,7 +4516,7 @@
         </is>
       </c>
       <c r="Q27" s="7">
-        <f>IF(P27="","",IFERROR(VLOOKUP(O27,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P27="","",IFERROR(VLOOKUP(O27,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R27" s="7">
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="Q28" s="7">
-        <f>IF(P28="","",IFERROR(VLOOKUP(O28,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P28="","",IFERROR(VLOOKUP(O28,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R28" s="7">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="Q29" s="151">
-        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R29" s="80">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="Q30" s="151">
-        <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R30" s="80">
@@ -4994,7 +4994,7 @@
       <c r="O31" s="149" t="n"/>
       <c r="P31" s="78" t="n"/>
       <c r="Q31" s="151">
-        <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R31" s="80">
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="Q32" s="26">
-        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R32" s="26">
@@ -5240,7 +5240,7 @@
         </is>
       </c>
       <c r="Q33" s="26">
-        <f>IF(P30="","",IFERROR(VLOOKUP(O30,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R33" s="26">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="Q34" s="26">
-        <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R34" s="26">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="Q35" s="26">
-        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R35" s="26">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="Q36" s="26">
-        <f>IF(P33="","",IFERROR(VLOOKUP(O33,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R36" s="26">
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="Q37" s="26">
-        <f>IF(P34="","",IFERROR(VLOOKUP(O34,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R37" s="26">
@@ -5897,7 +5897,7 @@
         </is>
       </c>
       <c r="Q38" s="26">
-        <f>IF(P35="","",IFERROR(VLOOKUP(O35,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R38" s="26">
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="Q39" s="26">
-        <f>IF(P36="","",IFERROR(VLOOKUP(O36,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R39" s="26">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="Q40" s="26">
-        <f>IF(P37="","",IFERROR(VLOOKUP(O37,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R40" s="26">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="Q41" s="26">
-        <f>IF(P38="","",IFERROR(VLOOKUP(O38,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R41" s="26">
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="Q42" s="26">
-        <f>IF(P39="","",IFERROR(VLOOKUP(O39,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R42" s="26">
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="Q43" s="26">
-        <f>IF(P40="","",IFERROR(VLOOKUP(O40,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R43" s="26">
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="Q44" s="26">
-        <f>IF(P41="","",IFERROR(VLOOKUP(O41,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R44" s="26">
@@ -6816,7 +6816,7 @@
         </is>
       </c>
       <c r="Q45" s="26">
-        <f>IF(P42="","",IFERROR(VLOOKUP(O42,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P45="","",IFERROR(VLOOKUP(O45,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R45" s="26">
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Q46" s="26">
-        <f>IF(P43="","",IFERROR(VLOOKUP(O43,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R46" s="26">
@@ -7078,7 +7078,7 @@
         </is>
       </c>
       <c r="Q47" s="26">
-        <f>IF(P44="","",IFERROR(VLOOKUP(O44,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R47" s="26">
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="Q48" s="26">
-        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P48="","",IFERROR(VLOOKUP(O48,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R48" s="26">
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="Q49" s="157">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R49" s="87">
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="Q50" s="157">
-        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P50="","",IFERROR(VLOOKUP(O50,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R50" s="87">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="Q51" s="18">
-        <f>IF(P46="","",IFERROR(VLOOKUP(O46,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R51" s="18">
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="Q52" s="18">
-        <f>IF(P47="","",IFERROR(VLOOKUP(O47,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P52="","",IFERROR(VLOOKUP(O52,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R52" s="18">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="Q53" s="7">
-        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE()),""))</f>
+        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
       <c r="R53" s="7">

--- a/RNR_수입원가_2026_20260506.xlsx
+++ b/RNR_수입원가_2026_20260506.xlsx
@@ -989,69 +989,62 @@
     <author>RNR 재무팀</author>
   </authors>
   <commentList>
-    <comment ref="S6" authorId="0" shapeId="0">
+    <comment ref="S7" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8543 — 디지털시네마 서버/IMB
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S10" authorId="0" shapeId="0">
+    <comment ref="S11" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
       </text>
     </comment>
-    <comment ref="S12" authorId="0" shapeId="0">
+    <comment ref="S13" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8543 — 디지털시네마 프로젝터
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S14" authorId="0" shapeId="0">
+    <comment ref="S15" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8414.59 — Projector cooling fan
 (WTO 협정세율 0%)</t>
       </text>
     </comment>
-    <comment ref="S15" authorId="0" shapeId="0">
+    <comment ref="S16" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
       </text>
     </comment>
-    <comment ref="S16" authorId="0" shapeId="0">
+    <comment ref="S17" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 Fedex 직통관 (관세사 미경유)</t>
       </text>
     </comment>
-    <comment ref="S18" authorId="0" shapeId="0">
+    <comment ref="S19" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8543 — 디지털시네마 서버/IMB
 (정보기술협정 양허품목)</t>
       </text>
     </comment>
-    <comment ref="S21" authorId="0" shapeId="0">
+    <comment ref="S22" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
       </text>
     </comment>
-    <comment ref="S23" authorId="0" shapeId="0">
+    <comment ref="S24" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 Fedex 직통관 (관세사 미경유)</t>
-      </text>
-    </comment>
-    <comment ref="S24" authorId="0" shapeId="0">
-      <text>
-        <t>ITA(정보기술협정) 관세면제
-HS 8543 — 디지털시네마 서버/IMB
-(정보기술협정 양허품목)</t>
       </text>
     </comment>
     <comment ref="S25" authorId="0" shapeId="0">
@@ -1062,6 +1055,13 @@
       </text>
     </comment>
     <comment ref="S26" authorId="0" shapeId="0">
+      <text>
+        <t>ITA(정보기술협정) 관세면제
+HS 8543 — 디지털시네마 서버/IMB
+(정보기술협정 양허품목)</t>
+      </text>
+    </comment>
+    <comment ref="S27" authorId="0" shapeId="0">
       <text>
         <t>ITA(정보기술협정) 관세면제
 HS 8518/8543 디지털시네마장비</t>
@@ -1612,63 +1612,63 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CPO678-1</t>
+          <t>IPO016</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>Integ Process Group</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>50% TT advance, 50% Net 30</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F5" s="143" t="n">
-        <v>45965</v>
+        <v>45881</v>
       </c>
       <c r="G5" s="144" t="n">
-        <v>46007</v>
+        <v>46146</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>139083</v>
+        <v>6800</v>
       </c>
       <c r="I5" s="145">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B5,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
       <c r="J5" s="9" t="n">
-        <v>212471386</v>
+        <v>0</v>
       </c>
       <c r="K5" s="9">
         <f>IFERROR(ROUND(H5*I5,0),0)</f>
         <v/>
       </c>
       <c r="L5" s="9">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B5,RemitTable2,10,FALSE),0)</f>
         <v/>
       </c>
       <c r="M5" s="9">
-        <f>IFERROR(VLOOKUP(B5,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B5,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>Projector</t>
+          <t>JNIOR Model 410 (20EA)</t>
         </is>
       </c>
       <c r="O5" s="144" t="n">
-        <v>46002</v>
+        <v>45905</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>1219925801471M</t>
+          <t>883504210357</t>
         </is>
       </c>
       <c r="Q5" s="7">
@@ -1680,50 +1680,48 @@
         <v/>
       </c>
       <c r="S5" s="9" t="n">
-        <v>1682291</v>
+        <v>0</v>
       </c>
       <c r="T5" s="9" t="n">
-        <v>20784342</v>
-      </c>
-      <c r="U5" s="143" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+        <v>954760</v>
+      </c>
+      <c r="U5" s="143" t="n">
+        <v>45905</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>다민관세사</t>
+          <t>인천세관</t>
         </is>
       </c>
       <c r="W5" s="9" t="n">
-        <v>149729</v>
+        <v>0</v>
       </c>
       <c r="X5" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="Y5" s="9" t="n">
-        <v>2470670</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="9">
         <f>S5+T5+W5</f>
         <v/>
       </c>
-      <c r="AA5" s="10">
-        <f>K5+L5+M5+IFERROR(VLOOKUP(B5,RemitTable2,9,FALSE()),0)+Y5+Z5</f>
+      <c r="AA5" s="175">
+        <f>K5+L5+M5+IFERROR(VLOOKUP(B5,RemitTable2,9,FALSE),0)+Y5+Z5</f>
         <v/>
       </c>
       <c r="AB5" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="10">
+        <v>20</v>
+      </c>
+      <c r="AC5" s="175">
         <f>ROUND(AA5/AB5,0)</f>
         <v/>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr">
@@ -1743,17 +1741,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>GPO451</t>
+          <t>CPO678-1</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1762,20 +1760,20 @@
         </is>
       </c>
       <c r="F6" s="143" t="n">
-        <v>45982</v>
+        <v>45965</v>
       </c>
       <c r="G6" s="144" t="n">
-        <v>46020</v>
+        <v>46007</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>9060</v>
+        <v>139083</v>
       </c>
       <c r="I6" s="145">
         <f>IFERROR(VLOOKUP(B6,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J6" s="9" t="n">
-        <v>18264679</v>
+        <v>212471386</v>
       </c>
       <c r="K6" s="9">
         <f>IFERROR(ROUND(H6*I6,0),0)</f>
@@ -1791,15 +1789,15 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>IMB/Server</t>
+          <t>Projector</t>
         </is>
       </c>
       <c r="O6" s="144" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>2317625939353M</t>
+          <t>1219925801471M</t>
         </is>
       </c>
       <c r="Q6" s="7">
@@ -1811,31 +1809,31 @@
         <v/>
       </c>
       <c r="S6" s="9" t="n">
-        <v>0</v>
+        <v>1682291</v>
       </c>
       <c r="T6" s="9" t="n">
-        <v>1352610</v>
+        <v>20784342</v>
       </c>
       <c r="U6" s="143" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>다민관세사</t>
         </is>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>149729</v>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y6" s="9" t="n">
-        <v>0</v>
+        <v>2470670</v>
       </c>
       <c r="Z6" s="9">
         <f>S6+T6+W6</f>
@@ -1874,39 +1872,39 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>CPO679</t>
+          <t>GPO451</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F7" s="143" t="n">
-        <v>45987</v>
+        <v>45982</v>
       </c>
       <c r="G7" s="144" t="n">
-        <v>46007</v>
+        <v>46020</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>4474</v>
+        <v>9060</v>
       </c>
       <c r="I7" s="145">
         <f>IFERROR(VLOOKUP(B7,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>212471386</v>
+        <v>18264679</v>
       </c>
       <c r="K7" s="9">
         <f>IFERROR(ROUND(H7*I7,0),0)</f>
@@ -1922,15 +1920,15 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>IMB/Server</t>
         </is>
       </c>
       <c r="O7" s="144" t="n">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>1421425100697M</t>
+          <t>2317625939353M</t>
         </is>
       </c>
       <c r="Q7" s="7">
@@ -1942,31 +1940,31 @@
         <v/>
       </c>
       <c r="S7" s="9" t="n">
-        <v>560630</v>
+        <v>0</v>
       </c>
       <c r="T7" s="9" t="n">
-        <v>756850</v>
+        <v>1352610</v>
       </c>
       <c r="U7" s="143" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t>아인관세사</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W7" s="9" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y7" s="9" t="n">
-        <v>590823</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="9">
         <f>S7+T7+W7</f>
@@ -1985,261 +1983,261 @@
       </c>
       <c r="AD7" s="3" t="inlineStr">
         <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>CPO679</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F8" s="143" t="n">
+        <v>45987</v>
+      </c>
+      <c r="G8" s="144" t="n">
+        <v>46007</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>4474</v>
+      </c>
+      <c r="I8" s="145">
+        <f>IFERROR(VLOOKUP(B8,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>212471386</v>
+      </c>
+      <c r="K8" s="9">
+        <f>IFERROR(ROUND(H8*I8,0),0)</f>
+        <v/>
+      </c>
+      <c r="L8" s="9">
+        <f>IFERROR(VLOOKUP(B8,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="9">
+        <f>IFERROR(VLOOKUP(B8,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="O8" s="144" t="n">
+        <v>45989</v>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>1421425100697M</t>
+        </is>
+      </c>
+      <c r="Q8" s="7">
+        <f>IF(P8="","",IFERROR(VLOOKUP(O8,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R8" s="7">
+        <f>IF(P8="","",H8)</f>
+        <v/>
+      </c>
+      <c r="S8" s="9" t="n">
+        <v>560630</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>756850</v>
+      </c>
+      <c r="U8" s="143" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>아인관세사</t>
+        </is>
+      </c>
+      <c r="W8" s="9" t="n">
+        <v>36000</v>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>진로직스</t>
+        </is>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>590823</v>
+      </c>
+      <c r="Z8" s="9">
+        <f>S8+T8+W8</f>
+        <v/>
+      </c>
+      <c r="AA8" s="10">
+        <f>K8+L8+M8+IFERROR(VLOOKUP(B8,RemitTable2,9,FALSE()),0)+Y8+Z8</f>
+        <v/>
+      </c>
+      <c r="AB8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="10">
+        <f>ROUND(AA8/AB8,0)</f>
+        <v/>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="AE7" s="3" t="inlineStr">
+      <c r="AE8" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>CPO684</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>부품</t>
         </is>
       </c>
-      <c r="F8" s="146" t="n">
+      <c r="F9" s="146" t="n">
         <v>45993</v>
       </c>
-      <c r="G8" s="147" t="inlineStr">
+      <c r="G9" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H9" s="16" t="n">
         <v>362.25</v>
       </c>
-      <c r="I8" s="148">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18">
-        <f>IFERROR(ROUND(H8*I8,0),0)</f>
-        <v/>
-      </c>
-      <c r="L8" s="18">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="18">
-        <f>IFERROR(VLOOKUP(B8,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="I9" s="148">
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <f>IFERROR(ROUND(H9*I9,0),0)</f>
+        <v/>
+      </c>
+      <c r="L9" s="18">
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="18">
+        <f>IFERROR(VLOOKUP(B9,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>Parts (국내)</t>
         </is>
       </c>
-      <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
-      <c r="Q8" s="18" t="n"/>
-      <c r="R8" s="18" t="n"/>
-      <c r="S8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="12" t="inlineStr">
+      <c r="O9" s="12" t="n"/>
+      <c r="P9" s="12" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="18" t="n"/>
+      <c r="S9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="13" t="inlineStr">
+      <c r="W9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y8" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="18">
-        <f>S8+T8+W8</f>
-        <v/>
-      </c>
-      <c r="AA8" s="18">
-        <f>K8+L8+M8+IFERROR(VLOOKUP(B8,RemitTable2,9,FALSE()),0)+Y8+Z8</f>
-        <v/>
-      </c>
-      <c r="AB8" s="19" t="n">
+      <c r="Y9" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="18">
+        <f>S9+T9+W9</f>
+        <v/>
+      </c>
+      <c r="AA9" s="18">
+        <f>K9+L9+M9+IFERROR(VLOOKUP(B9,RemitTable2,9,FALSE()),0)+Y9+Z9</f>
+        <v/>
+      </c>
+      <c r="AB9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="AC8" s="18">
-        <f>ROUND(AA8/AB8,0)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="12" t="n"/>
-      <c r="AE8" s="12" t="inlineStr">
+      <c r="AC9" s="18">
+        <f>ROUND(AA9/AB9,0)</f>
+        <v/>
+      </c>
+      <c r="AD9" s="12" t="n"/>
+      <c r="AE9" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF8" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>CPO680</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>부품</t>
-        </is>
-      </c>
-      <c r="F9" s="143" t="n">
-        <v>45995</v>
-      </c>
-      <c r="G9" s="144" t="n">
-        <v>46035</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>252</v>
-      </c>
-      <c r="I9" s="145">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="9" t="n">
-        <v>412788</v>
-      </c>
-      <c r="K9" s="9">
-        <f>IFERROR(ROUND(H9*I9,0),0)</f>
-        <v/>
-      </c>
-      <c r="L9" s="9">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="9">
-        <f>IFERROR(VLOOKUP(B9,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>Parts</t>
-        </is>
-      </c>
-      <c r="O9" s="144" t="n">
-        <v>46002</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>1219925801471M</t>
-        </is>
-      </c>
-      <c r="Q9" s="7">
-        <f>IF(P9="","",IFERROR(VLOOKUP(O9,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R9" s="7">
-        <f>IF(P9="","",H9)</f>
-        <v/>
-      </c>
-      <c r="S9" s="9" t="n">
-        <v>29879</v>
-      </c>
-      <c r="T9" s="9" t="n">
-        <v>37658</v>
-      </c>
-      <c r="U9" s="143" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>다민관세사</t>
-        </is>
-      </c>
-      <c r="W9" s="9" t="n">
-        <v>271</v>
-      </c>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>진로직스</t>
-        </is>
-      </c>
-      <c r="Y9" s="9" t="n">
-        <v>4477</v>
-      </c>
-      <c r="Z9" s="9">
-        <f>S9+T9+W9</f>
-        <v/>
-      </c>
-      <c r="AA9" s="10">
-        <f>K9+L9+M9+IFERROR(VLOOKUP(B9,RemitTable2,9,FALSE()),0)+Y9+Z9</f>
-        <v/>
-      </c>
-      <c r="AB9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="10">
-        <f>ROUND(AA9/AB9,0)</f>
-        <v/>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AF9" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2251,39 +2249,39 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>GPO460</t>
+          <t>CPO680</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F10" s="143" t="n">
-        <v>46007</v>
+        <v>45995</v>
       </c>
       <c r="G10" s="144" t="n">
-        <v>46043</v>
+        <v>46035</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>2710</v>
+        <v>252</v>
       </c>
       <c r="I10" s="145">
         <f>IFERROR(VLOOKUP(B10,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>5505104</v>
+        <v>412788</v>
       </c>
       <c r="K10" s="9">
         <f>IFERROR(ROUND(H10*I10,0),0)</f>
@@ -2299,15 +2297,15 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>SR-1000</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="O10" s="144" t="n">
-        <v>46023</v>
+        <v>46002</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>2317626006259M</t>
+          <t>1219925801471M</t>
         </is>
       </c>
       <c r="Q10" s="7">
@@ -2319,31 +2317,31 @@
         <v/>
       </c>
       <c r="S10" s="9" t="n">
-        <v>0</v>
+        <v>29879</v>
       </c>
       <c r="T10" s="9" t="n">
-        <v>399770</v>
+        <v>37658</v>
       </c>
       <c r="U10" s="143" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>다민관세사</t>
         </is>
       </c>
       <c r="W10" s="9" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y10" s="9" t="n">
-        <v>0</v>
+        <v>4477</v>
       </c>
       <c r="Z10" s="9">
         <f>S10+T10+W10</f>
@@ -2362,7 +2360,7 @@
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE10" s="3" t="inlineStr">
@@ -2382,17 +2380,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>LPO001</t>
+          <t>GPO460</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Lemon</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>TT Advance</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -2404,17 +2402,17 @@
         <v>46007</v>
       </c>
       <c r="G11" s="144" t="n">
-        <v>46052</v>
+        <v>46043</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>5056.8</v>
+        <v>2710</v>
       </c>
       <c r="I11" s="145">
         <f>IFERROR(VLOOKUP(B11,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>7356514</v>
+        <v>5505104</v>
       </c>
       <c r="K11" s="9">
         <f>IFERROR(ROUND(H11*I11,0),0)</f>
@@ -2430,15 +2428,15 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>ICP+TPC (6EA)</t>
+          <t>SR-1000</t>
         </is>
       </c>
       <c r="O11" s="144" t="n">
-        <v>46090</v>
+        <v>46023</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>1421426100183M</t>
+          <t>2317626006259M</t>
         </is>
       </c>
       <c r="Q11" s="7">
@@ -2450,31 +2448,31 @@
         <v/>
       </c>
       <c r="S11" s="9" t="n">
-        <v>240450</v>
+        <v>0</v>
       </c>
       <c r="T11" s="9" t="n">
-        <v>831820</v>
+        <v>399770</v>
       </c>
       <c r="U11" s="143" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t>아인관세사</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W11" s="9" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y11" s="9" t="n">
-        <v>581438</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="9">
         <f>S11+T11+W11</f>
@@ -2485,7 +2483,7 @@
         <v/>
       </c>
       <c r="AB11" s="11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC11" s="10">
         <f>ROUND(AA11/AB11,0)</f>
@@ -2493,7 +2491,7 @@
       </c>
       <c r="AD11" s="3" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE11" s="3" t="inlineStr">
@@ -2513,17 +2511,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>CPO678-2</t>
+          <t>LPO001</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>Lemon</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>TT Advance</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -2532,20 +2530,20 @@
         </is>
       </c>
       <c r="F12" s="143" t="n">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="G12" s="144" t="n">
-        <v>46087</v>
+        <v>46052</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>137850</v>
+        <v>5056.8</v>
       </c>
       <c r="I12" s="145">
         <f>IFERROR(VLOOKUP(B12,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>203737212</v>
+        <v>7356514</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(ROUND(H12*I12,0),0)</f>
@@ -2561,15 +2559,15 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>CP4425-RGB Projector (3EA)</t>
+          <t>ICP+TPC (6EA)</t>
         </is>
       </c>
       <c r="O12" s="144" t="n">
-        <v>46030</v>
+        <v>46090</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>1400826101004M</t>
+          <t>1421426100183M</t>
         </is>
       </c>
       <c r="Q12" s="7">
@@ -2581,23 +2579,23 @@
         <v/>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0</v>
+        <v>240450</v>
       </c>
       <c r="T12" s="9" t="n">
-        <v>19976300</v>
+        <v>831820</v>
       </c>
       <c r="U12" s="143" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t>조운관세사</t>
+          <t>아인관세사</t>
         </is>
       </c>
       <c r="W12" s="9" t="n">
-        <v>263400</v>
+        <v>36000</v>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
@@ -2605,7 +2603,7 @@
         </is>
       </c>
       <c r="Y12" s="9" t="n">
-        <v>2385057</v>
+        <v>581438</v>
       </c>
       <c r="Z12" s="9">
         <f>S12+T12+W12</f>
@@ -2616,7 +2614,7 @@
         <v/>
       </c>
       <c r="AB12" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC12" s="10">
         <f>ROUND(AA12/AB12,0)</f>
@@ -2624,7 +2622,7 @@
       </c>
       <c r="AD12" s="3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="AE12" s="3" t="inlineStr">
@@ -2644,7 +2642,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>CPO682</t>
+          <t>CPO678-2</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2663,20 +2661,20 @@
         </is>
       </c>
       <c r="F13" s="143" t="n">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="G13" s="144" t="n">
-        <v>46057</v>
+        <v>46087</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>20174</v>
+        <v>137850</v>
       </c>
       <c r="I13" s="145">
         <f>IFERROR(VLOOKUP(B13,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>36117425</v>
+        <v>203737212</v>
       </c>
       <c r="K13" s="9">
         <f>IFERROR(ROUND(H13*I13,0),0)</f>
@@ -2692,15 +2690,15 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Projector + Touch Screen (2EA)</t>
+          <t>CP4425-RGB Projector (3EA)</t>
         </is>
       </c>
       <c r="O13" s="144" t="n">
-        <v>46015</v>
+        <v>46030</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>1400825101450M</t>
+          <t>1400826101004M</t>
         </is>
       </c>
       <c r="Q13" s="7">
@@ -2712,23 +2710,23 @@
         <v/>
       </c>
       <c r="S13" s="9" t="n">
-        <v>84170</v>
+        <v>0</v>
       </c>
       <c r="T13" s="9" t="n">
-        <v>3156262</v>
+        <v>19976300</v>
       </c>
       <c r="U13" s="143" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>아인관세사</t>
+          <t>조운관세사</t>
         </is>
       </c>
       <c r="W13" s="9" t="n">
-        <v>92978</v>
+        <v>263400</v>
       </c>
       <c r="X13" s="4" t="inlineStr">
         <is>
@@ -2736,7 +2734,7 @@
         </is>
       </c>
       <c r="Y13" s="9" t="n">
-        <v>1864148</v>
+        <v>2385057</v>
       </c>
       <c r="Z13" s="9">
         <f>S13+T13+W13</f>
@@ -2747,7 +2745,7 @@
         <v/>
       </c>
       <c r="AB13" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC13" s="10">
         <f>ROUND(AA13/AB13,0)</f>
@@ -2755,7 +2753,7 @@
       </c>
       <c r="AD13" s="3" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE13" s="3" t="inlineStr">
@@ -2775,7 +2773,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>CPO683</t>
+          <t>CPO682</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -2800,7 +2798,7 @@
         <v>46057</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4620</v>
+        <v>20174</v>
       </c>
       <c r="I14" s="145">
         <f>IFERROR(VLOOKUP(B14,RemitTable2,7,FALSE()),0)</f>
@@ -2823,7 +2821,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>Fan (15EA)</t>
+          <t>Projector + Touch Screen (2EA)</t>
         </is>
       </c>
       <c r="O14" s="144" t="n">
@@ -2843,10 +2841,10 @@
         <v/>
       </c>
       <c r="S14" s="9" t="n">
-        <v>0</v>
+        <v>84170</v>
       </c>
       <c r="T14" s="9" t="n">
-        <v>722808</v>
+        <v>3156262</v>
       </c>
       <c r="U14" s="143" t="inlineStr">
         <is>
@@ -2859,7 +2857,7 @@
         </is>
       </c>
       <c r="W14" s="9" t="n">
-        <v>14422</v>
+        <v>92978</v>
       </c>
       <c r="X14" s="4" t="inlineStr">
         <is>
@@ -2867,7 +2865,7 @@
         </is>
       </c>
       <c r="Y14" s="9" t="n">
-        <v>426904</v>
+        <v>1864148</v>
       </c>
       <c r="Z14" s="9">
         <f>S14+T14+W14</f>
@@ -2906,17 +2904,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>MPO66</t>
+          <t>CPO683</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>T/T</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -2925,20 +2923,20 @@
         </is>
       </c>
       <c r="F15" s="143" t="n">
-        <v>46011</v>
+        <v>46010</v>
       </c>
       <c r="G15" s="144" t="n">
-        <v>46043</v>
+        <v>46057</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>9626.35</v>
+        <v>4620</v>
       </c>
       <c r="I15" s="145">
         <f>IFERROR(VLOOKUP(B15,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>14256012</v>
+        <v>36117425</v>
       </c>
       <c r="K15" s="9">
         <f>IFERROR(ROUND(H15*I15,0),0)</f>
@@ -2954,15 +2952,15 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>DCO-16000/L-SUB (13EA)</t>
+          <t>Fan (15EA)</t>
         </is>
       </c>
       <c r="O15" s="144" t="n">
-        <v>46072</v>
+        <v>46015</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>1421426100153M</t>
+          <t>1400825101450M</t>
         </is>
       </c>
       <c r="Q15" s="7">
@@ -2977,11 +2975,11 @@
         <v>0</v>
       </c>
       <c r="T15" s="9" t="n">
-        <v>1704871</v>
+        <v>722808</v>
       </c>
       <c r="U15" s="143" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
@@ -2990,7 +2988,7 @@
         </is>
       </c>
       <c r="W15" s="9" t="n">
-        <v>93591</v>
+        <v>14422</v>
       </c>
       <c r="X15" s="4" t="inlineStr">
         <is>
@@ -2998,7 +2996,7 @@
         </is>
       </c>
       <c r="Y15" s="9" t="n">
-        <v>2690702</v>
+        <v>426904</v>
       </c>
       <c r="Z15" s="9">
         <f>S15+T15+W15</f>
@@ -3009,7 +3007,7 @@
         <v/>
       </c>
       <c r="AB15" s="11" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AC15" s="10">
         <f>ROUND(AA15/AB15,0)</f>
@@ -3017,7 +3015,7 @@
       </c>
       <c r="AD15" s="3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE15" s="3" t="inlineStr">
@@ -3037,7 +3035,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>MPO65</t>
+          <t>MPO66</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -3059,17 +3057,17 @@
         <v>46011</v>
       </c>
       <c r="G16" s="144" t="n">
-        <v>46007</v>
+        <v>46043</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>4936</v>
+        <v>9626.35</v>
       </c>
       <c r="I16" s="145">
         <f>IFERROR(VLOOKUP(B16,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>22306800</v>
+        <v>14256012</v>
       </c>
       <c r="K16" s="9">
         <f>IFERROR(ROUND(H16*I16,0),0)</f>
@@ -3085,7 +3083,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Audio Amp</t>
+          <t>DCO-16000/L-SUB (13EA)</t>
         </is>
       </c>
       <c r="O16" s="144" t="n">
@@ -3108,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="9" t="n">
-        <v>874189</v>
+        <v>1704871</v>
       </c>
       <c r="U16" s="143" t="inlineStr">
         <is>
@@ -3121,7 +3119,7 @@
         </is>
       </c>
       <c r="W16" s="9" t="n">
-        <v>47990</v>
+        <v>93591</v>
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
@@ -3129,7 +3127,7 @@
         </is>
       </c>
       <c r="Y16" s="9" t="n">
-        <v>1379682</v>
+        <v>2690702</v>
       </c>
       <c r="Z16" s="9">
         <f>S16+T16+W16</f>
@@ -3140,7 +3138,7 @@
         <v/>
       </c>
       <c r="AB16" s="11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AC16" s="10">
         <f>ROUND(AA16/AB16,0)</f>
@@ -3168,39 +3166,39 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>CPO689</t>
+          <t>MPO65</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>T/T</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F17" s="143" t="n">
-        <v>46025</v>
+        <v>46011</v>
       </c>
       <c r="G17" s="144" t="n">
-        <v>46072</v>
+        <v>46007</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>2745</v>
+        <v>4936</v>
       </c>
       <c r="I17" s="145">
         <f>IFERROR(VLOOKUP(B17,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>25506948</v>
+        <v>22306800</v>
       </c>
       <c r="K17" s="9">
         <f>IFERROR(ROUND(H17*I17,0),0)</f>
@@ -3216,15 +3214,15 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>Parts</t>
+          <t>Audio Amp</t>
         </is>
       </c>
       <c r="O17" s="144" t="n">
-        <v>46042</v>
+        <v>46072</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>2317626055855M</t>
+          <t>1421426100153M</t>
         </is>
       </c>
       <c r="Q17" s="7">
@@ -3236,31 +3234,31 @@
         <v/>
       </c>
       <c r="S17" s="9" t="n">
-        <v>20430</v>
+        <v>0</v>
       </c>
       <c r="T17" s="9" t="n">
-        <v>409790</v>
+        <v>874189</v>
       </c>
       <c r="U17" s="143" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아인관세사</t>
         </is>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
+        <v>47990</v>
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y17" s="9" t="n">
-        <v>162080</v>
+        <v>1379682</v>
       </c>
       <c r="Z17" s="9">
         <f>S17+T17+W17</f>
@@ -3279,7 +3277,7 @@
       </c>
       <c r="AD17" s="3" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="AE17" s="3" t="inlineStr">
@@ -3299,39 +3297,39 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>GPO467</t>
+          <t>CPO689</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F18" s="143" t="n">
-        <v>46029</v>
+        <v>46025</v>
       </c>
       <c r="G18" s="144" t="n">
-        <v>46113</v>
+        <v>46072</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1700</v>
+        <v>2745</v>
       </c>
       <c r="I18" s="145">
         <f>IFERROR(VLOOKUP(B18,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>9919642</v>
+        <v>25506948</v>
       </c>
       <c r="K18" s="9">
         <f>IFERROR(ROUND(H18*I18,0),0)</f>
@@ -3347,15 +3345,15 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>SR-1000 Face Plate(20)+Security Gate(10)</t>
+          <t>Parts</t>
         </is>
       </c>
       <c r="O18" s="144" t="n">
-        <v>46056</v>
+        <v>46042</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>2317626105219M</t>
+          <t>2317626055855M</t>
         </is>
       </c>
       <c r="Q18" s="7">
@@ -3367,14 +3365,14 @@
         <v/>
       </c>
       <c r="S18" s="9" t="n">
-        <v>0</v>
+        <v>20430</v>
       </c>
       <c r="T18" s="9" t="n">
-        <v>250080</v>
+        <v>409790</v>
       </c>
       <c r="U18" s="143" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
@@ -3391,7 +3389,7 @@
         </is>
       </c>
       <c r="Y18" s="9" t="n">
-        <v>136050</v>
+        <v>162080</v>
       </c>
       <c r="Z18" s="9">
         <f>S18+T18+W18</f>
@@ -3402,7 +3400,7 @@
         <v/>
       </c>
       <c r="AB18" s="11" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="10">
         <f>ROUND(AA18/AB18,0)</f>
@@ -3410,7 +3408,7 @@
       </c>
       <c r="AD18" s="3" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE18" s="3" t="inlineStr">
@@ -3430,59 +3428,63 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>CPO692-1</t>
+          <t>GPO467</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>부품(렌즈)</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F19" s="143" t="n">
-        <v>46035</v>
+        <v>46029</v>
       </c>
       <c r="G19" s="144" t="n">
-        <v>46134</v>
+        <v>46113</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>11000</v>
-      </c>
-      <c r="I19" s="145" t="n">
-        <v>1482.8</v>
+        <v>1700</v>
+      </c>
+      <c r="I19" s="145">
+        <f>IFERROR(VLOOKUP(B19,RemitTable2,7,FALSE()),0)</f>
+        <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>16310800</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>16310800</v>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>462</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>296</v>
+        <v>9919642</v>
+      </c>
+      <c r="K19" s="9">
+        <f>IFERROR(ROUND(H19*I19,0),0)</f>
+        <v/>
+      </c>
+      <c r="L19" s="9">
+        <f>IFERROR(VLOOKUP(B19,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M19" s="9">
+        <f>IFERROR(VLOOKUP(B19,RemitTable2,11,FALSE()),0)</f>
+        <v/>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>Lens (2EA)</t>
+          <t>SR-1000 Face Plate(20)+Security Gate(10)</t>
         </is>
       </c>
       <c r="O19" s="144" t="n">
-        <v>46064</v>
+        <v>46056</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>2235626138790M</t>
+          <t>2317626105219M</t>
         </is>
       </c>
       <c r="Q19" s="7">
@@ -3494,14 +3496,14 @@
         <v/>
       </c>
       <c r="S19" s="9" t="n">
-        <v>1297810</v>
+        <v>0</v>
       </c>
       <c r="T19" s="9" t="n">
-        <v>1752040</v>
+        <v>250080</v>
       </c>
       <c r="U19" s="143" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
@@ -3514,24 +3516,26 @@
       </c>
       <c r="X19" s="4" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y19" s="9" t="n">
-        <v>1553086</v>
+        <v>136050</v>
       </c>
       <c r="Z19" s="9">
         <f>S19+T19+W19</f>
         <v/>
       </c>
-      <c r="AA19" s="10" t="n">
-        <v>20915590</v>
+      <c r="AA19" s="10">
+        <f>K19+L19+M19+IFERROR(VLOOKUP(B19,RemitTable2,9,FALSE()),0)+Y19+Z19</f>
+        <v/>
       </c>
       <c r="AB19" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC19" s="10" t="n">
-        <v>10457795</v>
+        <v>30</v>
+      </c>
+      <c r="AC19" s="10">
+        <f>ROUND(AA19/AB19,0)</f>
+        <v/>
       </c>
       <c r="AD19" s="3" t="inlineStr">
         <is>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>CPO692-2</t>
+          <t>CPO692-1</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -3570,7 +3574,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품(렌즈)</t>
         </is>
       </c>
       <c r="F20" s="143" t="n">
@@ -3580,34 +3584,34 @@
         <v>46134</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>286580</v>
+        <v>11000</v>
       </c>
       <c r="I20" s="145" t="n">
         <v>1482.8</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>424990980</v>
+        <v>16310800</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>424990980</v>
+        <v>16310800</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>12038</v>
+        <v>462</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>7704</v>
+        <v>296</v>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>Projector+Lens+ASSY (28EA)</t>
+          <t>Lens (2EA)</t>
         </is>
       </c>
       <c r="O20" s="144" t="n">
-        <v>46073</v>
+        <v>46064</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>1400826101051M</t>
+          <t>2235626138790M</t>
         </is>
       </c>
       <c r="Q20" s="7">
@@ -3619,44 +3623,44 @@
         <v/>
       </c>
       <c r="S20" s="9" t="n">
-        <v>3450410</v>
+        <v>1297810</v>
       </c>
       <c r="T20" s="9" t="n">
-        <v>42329590</v>
+        <v>1752040</v>
       </c>
       <c r="U20" s="143" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>조운관세사</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W20" s="9" t="n">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="X20" s="4" t="inlineStr">
         <is>
-          <t>진로직스</t>
+          <t>DHL</t>
         </is>
       </c>
       <c r="Y20" s="9" t="n">
-        <v>2649525</v>
+        <v>1553086</v>
       </c>
       <c r="Z20" s="9">
         <f>S20+T20+W20</f>
         <v/>
       </c>
       <c r="AA20" s="10" t="n">
-        <v>473718807</v>
+        <v>20915590</v>
       </c>
       <c r="AB20" s="11" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC20" s="10" t="n">
-        <v>16918529</v>
+        <v>10457795</v>
       </c>
       <c r="AD20" s="3" t="inlineStr">
         <is>
@@ -3680,7 +3684,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>CPO690</t>
+          <t>CPO692-2</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -3695,48 +3699,44 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F21" s="143" t="n">
-        <v>46050</v>
+        <v>46035</v>
       </c>
       <c r="G21" s="144" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>9740</v>
-      </c>
-      <c r="I21" s="145">
-        <f>IFERROR(VLOOKUP(B21,RemitTable2,7,FALSE()),0)</f>
-        <v/>
+        <v>286580</v>
+      </c>
+      <c r="I21" s="145" t="n">
+        <v>1482.8</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>51777431</v>
-      </c>
-      <c r="K21" s="9">
-        <f>IFERROR(ROUND(H21*I21,0),0)</f>
-        <v/>
-      </c>
-      <c r="L21" s="9">
-        <f>IFERROR(VLOOKUP(B21,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="9">
-        <f>IFERROR(VLOOKUP(B21,RemitTable2,11,FALSE()),0)</f>
-        <v/>
+        <v>424990980</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>424990980</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>12038</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>7704</v>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>ASSY Liquid Cooling (20EA)</t>
+          <t>Projector+Lens+ASSY (28EA)</t>
         </is>
       </c>
       <c r="O21" s="144" t="n">
-        <v>46053</v>
+        <v>46073</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>2235626096487M</t>
+          <t>1400826101051M</t>
         </is>
       </c>
       <c r="Q21" s="7">
@@ -3748,306 +3748,302 @@
         <v/>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
+        <v>3450410</v>
       </c>
       <c r="T21" s="9" t="n">
-        <v>1493440</v>
+        <v>42329590</v>
       </c>
       <c r="U21" s="143" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>조운관세사</t>
         </is>
       </c>
       <c r="W21" s="9" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y21" s="9" t="n">
-        <v>1561040</v>
+        <v>2649525</v>
       </c>
       <c r="Z21" s="9">
         <f>S21+T21+W21</f>
         <v/>
       </c>
-      <c r="AA21" s="10">
-        <f>K21+L21+M21+IFERROR(VLOOKUP(B21,RemitTable2,9,FALSE()),0)+Y21+Z21</f>
-        <v/>
+      <c r="AA21" s="10" t="n">
+        <v>473718807</v>
       </c>
       <c r="AB21" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC21" s="10" t="n">
+        <v>16918529</v>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>CPO690</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F22" s="143" t="n">
+        <v>46050</v>
+      </c>
+      <c r="G22" s="144" t="n">
+        <v>46113</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>9740</v>
+      </c>
+      <c r="I22" s="145">
+        <f>IFERROR(VLOOKUP(B22,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>51777431</v>
+      </c>
+      <c r="K22" s="9">
+        <f>IFERROR(ROUND(H22*I22,0),0)</f>
+        <v/>
+      </c>
+      <c r="L22" s="9">
+        <f>IFERROR(VLOOKUP(B22,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="9">
+        <f>IFERROR(VLOOKUP(B22,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>ASSY Liquid Cooling (20EA)</t>
+        </is>
+      </c>
+      <c r="O22" s="144" t="n">
+        <v>46053</v>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>2235626096487M</t>
+        </is>
+      </c>
+      <c r="Q22" s="7">
+        <f>IF(P22="","",IFERROR(VLOOKUP(O22,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R22" s="7">
+        <f>IF(P22="","",H22)</f>
+        <v/>
+      </c>
+      <c r="S22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>1493440</v>
+      </c>
+      <c r="U22" s="143" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="4" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>1561040</v>
+      </c>
+      <c r="Z22" s="9">
+        <f>S22+T22+W22</f>
+        <v/>
+      </c>
+      <c r="AA22" s="10">
+        <f>K22+L22+M22+IFERROR(VLOOKUP(B22,RemitTable2,9,FALSE()),0)+Y22+Z22</f>
+        <v/>
+      </c>
+      <c r="AB22" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="AC21" s="10">
-        <f>ROUND(AA21/AB21,0)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="3" t="inlineStr">
+      <c r="AC22" s="10">
+        <f>ROUND(AA22/AB22,0)</f>
+        <v/>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="AE21" s="3" t="inlineStr">
+      <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>CPO693</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>장비</t>
         </is>
       </c>
-      <c r="F22" s="146" t="n">
+      <c r="F23" s="146" t="n">
         <v>46071</v>
       </c>
-      <c r="G22" s="147" t="inlineStr">
+      <c r="G23" s="147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H23" s="16" t="n">
         <v>35674</v>
       </c>
-      <c r="I22" s="148">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="18">
-        <f>IFERROR(ROUND(H22*I22,0),0)</f>
-        <v/>
-      </c>
-      <c r="L22" s="18">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="18">
-        <f>IFERROR(VLOOKUP(B22,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N22" s="12" t="inlineStr">
+      <c r="I23" s="148">
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="18">
+        <f>IFERROR(ROUND(H23*I23,0),0)</f>
+        <v/>
+      </c>
+      <c r="L23" s="18">
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="18">
+        <f>IFERROR(VLOOKUP(B23,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12" t="inlineStr">
         <is>
           <t>Projector (한국)</t>
         </is>
       </c>
-      <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
-      <c r="Q22" s="18" t="n"/>
-      <c r="R22" s="18" t="n"/>
-      <c r="S22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="12" t="inlineStr">
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="12" t="n"/>
+      <c r="Q23" s="18" t="n"/>
+      <c r="R23" s="18" t="n"/>
+      <c r="S23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="13" t="inlineStr">
+      <c r="W23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y22" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="18">
-        <f>S22+T22+W22</f>
-        <v/>
-      </c>
-      <c r="AA22" s="18">
-        <f>K22+L22+M22+IFERROR(VLOOKUP(B22,RemitTable2,9,FALSE()),0)+Y22+Z22</f>
-        <v/>
-      </c>
-      <c r="AB22" s="19" t="n">
+      <c r="Y23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="18">
+        <f>S23+T23+W23</f>
+        <v/>
+      </c>
+      <c r="AA23" s="18">
+        <f>K23+L23+M23+IFERROR(VLOOKUP(B23,RemitTable2,9,FALSE()),0)+Y23+Z23</f>
+        <v/>
+      </c>
+      <c r="AB23" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="AC22" s="18">
-        <f>ROUND(AA22/AB22,0)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="12" t="n"/>
-      <c r="AE22" s="12" t="inlineStr">
+      <c r="AC23" s="18">
+        <f>ROUND(AA23/AB23,0)</f>
+        <v/>
+      </c>
+      <c r="AD23" s="12" t="n"/>
+      <c r="AE23" s="12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF22" s="13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>GPO468-1</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>GDC</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Net 30 days</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>장비</t>
-        </is>
-      </c>
-      <c r="F23" s="143" t="n">
-        <v>46080</v>
-      </c>
-      <c r="G23" s="144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>36190</v>
-      </c>
-      <c r="I23" s="145">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="9">
-        <f>IFERROR(ROUND(H23*I23,0),0)</f>
-        <v/>
-      </c>
-      <c r="L23" s="9">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="9">
-        <f>IFERROR(VLOOKUP(B23,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>SR-1000 IMB (10EA)</t>
-        </is>
-      </c>
-      <c r="O23" s="144" t="n">
-        <v>46095</v>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>1400826101085M</t>
-        </is>
-      </c>
-      <c r="Q23" s="7">
-        <f>IF(P23="","",IFERROR(VLOOKUP(O23,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R23" s="7">
-        <f>IF(P23="","",H23)</f>
-        <v/>
-      </c>
-      <c r="S23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="9" t="n">
-        <v>5395574</v>
-      </c>
-      <c r="U23" s="143" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>조운관세사</t>
-        </is>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>137864</v>
-      </c>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>진로직스</t>
-        </is>
-      </c>
-      <c r="Y23" s="9" t="n">
-        <v>1232133</v>
-      </c>
-      <c r="Z23" s="9">
-        <f>S23+T23+W23</f>
-        <v/>
-      </c>
-      <c r="AA23" s="10">
-        <f>K23+L23+M23+IFERROR(VLOOKUP(B23,RemitTable2,9,FALSE()),0)+Y23+Z23</f>
-        <v/>
-      </c>
-      <c r="AB23" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC23" s="10">
-        <f>ROUND(AA23/AB23,0)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="AE23" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AF23" s="13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4059,7 +4055,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>GPO472</t>
+          <t>GPO468-1</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -4074,11 +4070,11 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F24" s="143" t="n">
-        <v>46088</v>
+        <v>46080</v>
       </c>
       <c r="G24" s="144" t="inlineStr">
         <is>
@@ -4086,7 +4082,7 @@
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>180</v>
+        <v>36190</v>
       </c>
       <c r="I24" s="145">
         <f>IFERROR(VLOOKUP(B24,RemitTable2,7,FALSE()),0)</f>
@@ -4109,7 +4105,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>SR-1000 Coverplate (3EA)</t>
+          <t>SR-1000 IMB (10EA)</t>
         </is>
       </c>
       <c r="O24" s="144" t="n">
@@ -4132,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="T24" s="9" t="n">
-        <v>26836</v>
+        <v>5395574</v>
       </c>
       <c r="U24" s="143" t="inlineStr">
         <is>
@@ -4145,7 +4141,7 @@
         </is>
       </c>
       <c r="W24" s="9" t="n">
-        <v>536</v>
+        <v>137864</v>
       </c>
       <c r="X24" s="4" t="inlineStr">
         <is>
@@ -4153,7 +4149,7 @@
         </is>
       </c>
       <c r="Y24" s="9" t="n">
-        <v>6128</v>
+        <v>1232133</v>
       </c>
       <c r="Z24" s="9">
         <f>S24+T24+W24</f>
@@ -4164,7 +4160,7 @@
         <v/>
       </c>
       <c r="AB24" s="11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AC24" s="10">
         <f>ROUND(AA24/AB24,0)</f>
@@ -4192,7 +4188,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GPO468-2</t>
+          <t>GPO472</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -4207,7 +4203,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>부품</t>
         </is>
       </c>
       <c r="F25" s="143" t="n">
@@ -4219,7 +4215,7 @@
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>21280</v>
+        <v>180</v>
       </c>
       <c r="I25" s="145">
         <f>IFERROR(VLOOKUP(B25,RemitTable2,7,FALSE()),0)</f>
@@ -4242,15 +4238,15 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>IMB</t>
+          <t>SR-1000 Coverplate (3EA)</t>
         </is>
       </c>
       <c r="O25" s="144" t="n">
-        <v>46104</v>
+        <v>46095</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>2317626258975M</t>
+          <t>1400826101085M</t>
         </is>
       </c>
       <c r="Q25" s="7">
@@ -4265,28 +4261,28 @@
         <v>0</v>
       </c>
       <c r="T25" s="9" t="n">
-        <v>4747530</v>
+        <v>26836</v>
       </c>
       <c r="U25" s="143" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>조운관세사</t>
         </is>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>536</v>
       </c>
       <c r="X25" s="4" t="inlineStr">
         <is>
-          <t>Fedex</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y25" s="9" t="n">
-        <v>904960</v>
+        <v>6128</v>
       </c>
       <c r="Z25" s="9">
         <f>S25+T25+W25</f>
@@ -4297,7 +4293,7 @@
         <v/>
       </c>
       <c r="AB25" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC25" s="10">
         <f>ROUND(AA25/AB25,0)</f>
@@ -4325,32 +4321,34 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>CPO695-1</t>
+          <t>GPO468-2</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>부품(Fan)</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F26" s="143" t="n">
-        <v>46098</v>
-      </c>
-      <c r="G26" s="144" t="n">
-        <v>46146</v>
+        <v>46088</v>
+      </c>
+      <c r="G26" s="144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>2058</v>
+        <v>21280</v>
       </c>
       <c r="I26" s="145">
         <f>IFERROR(VLOOKUP(B26,RemitTable2,7,FALSE()),0)</f>
@@ -4373,15 +4371,15 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>Fan (7EA)</t>
+          <t>IMB</t>
         </is>
       </c>
       <c r="O26" s="144" t="n">
-        <v>46105</v>
+        <v>46104</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>2235626283517M</t>
+          <t>2317626258975M</t>
         </is>
       </c>
       <c r="Q26" s="7">
@@ -4396,16 +4394,16 @@
         <v>0</v>
       </c>
       <c r="T26" s="9" t="n">
-        <v>350480</v>
+        <v>4747530</v>
       </c>
       <c r="U26" s="143" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>운서합동</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W26" s="9" t="n">
@@ -4413,11 +4411,11 @@
       </c>
       <c r="X26" s="4" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>Fedex</t>
         </is>
       </c>
       <c r="Y26" s="9" t="n">
-        <v>6264783</v>
+        <v>904960</v>
       </c>
       <c r="Z26" s="9">
         <f>S26+T26+W26</f>
@@ -4428,7 +4426,7 @@
         <v/>
       </c>
       <c r="AB26" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AC26" s="10">
         <f>ROUND(AA26/AB26,0)</f>
@@ -4456,7 +4454,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CPO695-2</t>
+          <t>CPO695-1</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -4471,7 +4469,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>부품(Filter)</t>
+          <t>부품(Fan)</t>
         </is>
       </c>
       <c r="F27" s="143" t="n">
@@ -4481,7 +4479,7 @@
         <v>46146</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1977</v>
+        <v>2058</v>
       </c>
       <c r="I27" s="145">
         <f>IFERROR(VLOOKUP(B27,RemitTable2,7,FALSE()),0)</f>
@@ -4504,15 +4502,15 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>Filter(11EA)+Fan(5EA)</t>
+          <t>Fan (7EA)</t>
         </is>
       </c>
       <c r="O27" s="144" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>2235626277307M</t>
+          <t>2235626283517M</t>
         </is>
       </c>
       <c r="Q27" s="7">
@@ -4524,14 +4522,14 @@
         <v/>
       </c>
       <c r="S27" s="9" t="n">
-        <v>50790</v>
+        <v>0</v>
       </c>
       <c r="T27" s="9" t="n">
-        <v>317310</v>
+        <v>350480</v>
       </c>
       <c r="U27" s="143" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
@@ -4548,7 +4546,7 @@
         </is>
       </c>
       <c r="Y27" s="9" t="n">
-        <v>1454605</v>
+        <v>6264783</v>
       </c>
       <c r="Z27" s="9">
         <f>S27+T27+W27</f>
@@ -4559,7 +4557,7 @@
         <v/>
       </c>
       <c r="AB27" s="11" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AC27" s="10">
         <f>ROUND(AA27/AB27,0)</f>
@@ -4587,7 +4585,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>CPO698</t>
+          <t>CPO695-2</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -4602,21 +4600,25 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>부품(렌즈)</t>
+          <t>부품(Filter)</t>
         </is>
       </c>
       <c r="F28" s="143" t="n">
-        <v>46106</v>
-      </c>
-      <c r="G28" s="144" t="n"/>
+        <v>46098</v>
+      </c>
+      <c r="G28" s="144" t="n">
+        <v>46146</v>
+      </c>
       <c r="H28" s="7" t="n">
-        <v>4290</v>
+        <v>1977</v>
       </c>
       <c r="I28" s="145">
         <f>IFERROR(VLOOKUP(B28,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
-      <c r="J28" s="9" t="n"/>
+      <c r="J28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="K28" s="9">
         <f>IFERROR(ROUND(H28*I28,0),0)</f>
         <v/>
@@ -4631,15 +4633,15 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Lens 1.62-2.7 (2EA)</t>
+          <t>Filter(11EA)+Fan(5EA)</t>
         </is>
       </c>
       <c r="O28" s="144" t="n">
-        <v>46122</v>
+        <v>46104</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>2235626346781M</t>
+          <t>2235626277307M</t>
         </is>
       </c>
       <c r="Q28" s="7">
@@ -4651,12 +4653,16 @@
         <v/>
       </c>
       <c r="S28" s="9" t="n">
-        <v>524320</v>
+        <v>50790</v>
       </c>
       <c r="T28" s="9" t="n">
-        <v>707830</v>
-      </c>
-      <c r="U28" s="143" t="n"/>
+        <v>317310</v>
+      </c>
+      <c r="U28" s="143" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
           <t>운서합동</t>
@@ -4671,7 +4677,7 @@
         </is>
       </c>
       <c r="Y28" s="9" t="n">
-        <v>0</v>
+        <v>1454605</v>
       </c>
       <c r="Z28" s="9">
         <f>S28+T28+W28</f>
@@ -4682,7 +4688,7 @@
         <v/>
       </c>
       <c r="AB28" s="11" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="AC28" s="10">
         <f>ROUND(AA28/AB28,0)</f>
@@ -4690,132 +4696,134 @@
       </c>
       <c r="AD28" s="3" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>CPO698</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>부품(렌즈)</t>
+        </is>
+      </c>
+      <c r="F29" s="143" t="n">
+        <v>46106</v>
+      </c>
+      <c r="G29" s="144" t="n"/>
+      <c r="H29" s="7" t="n">
+        <v>4290</v>
+      </c>
+      <c r="I29" s="145">
+        <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9">
+        <f>IFERROR(ROUND(H29*I29,0),0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="9">
+        <f>IFERROR(VLOOKUP(B29,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="9">
+        <f>IFERROR(VLOOKUP(B29,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Lens 1.62-2.7 (2EA)</t>
+        </is>
+      </c>
+      <c r="O29" s="144" t="n">
+        <v>46122</v>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>2235626346781M</t>
+        </is>
+      </c>
+      <c r="Q29" s="7">
+        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R29" s="7">
+        <f>IF(P29="","",H29)</f>
+        <v/>
+      </c>
+      <c r="S29" s="9" t="n">
+        <v>524320</v>
+      </c>
+      <c r="T29" s="9" t="n">
+        <v>707830</v>
+      </c>
+      <c r="U29" s="143" t="n"/>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>운서합동</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="9">
+        <f>S29+T29+W29</f>
+        <v/>
+      </c>
+      <c r="AA29" s="10">
+        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE()),0)+Y29+Z29</f>
+        <v/>
+      </c>
+      <c r="AB29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC29" s="10">
+        <f>ROUND(AA29/AB29,0)</f>
+        <v/>
+      </c>
+      <c r="AD29" s="3" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE28" s="3" t="n"/>
-      <c r="AF28" s="4" t="n"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="78" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="78" t="inlineStr">
-        <is>
-          <t>CPO696-1</t>
-        </is>
-      </c>
-      <c r="C29" s="78" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D29" s="78" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E29" s="78" t="inlineStr">
-        <is>
-          <t>장비</t>
-        </is>
-      </c>
-      <c r="F29" s="149" t="n">
-        <v>46113</v>
-      </c>
-      <c r="G29" s="149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="80" t="n">
-        <v>78209</v>
-      </c>
-      <c r="I29" s="150">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="82">
-        <f>IFERROR(ROUND(H29*I29,0),0)</f>
-        <v/>
-      </c>
-      <c r="L29" s="82">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="82">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N29" s="78" t="inlineStr">
-        <is>
-          <t>CP4445-RGB Projector 외 (렌탈용)</t>
-        </is>
-      </c>
-      <c r="O29" s="149" t="n">
-        <v>46129</v>
-      </c>
-      <c r="P29" s="78" t="inlineStr">
-        <is>
-          <t>14008-26-101125M</t>
-        </is>
-      </c>
-      <c r="Q29" s="151">
-        <f>IF(P29="","",IFERROR(VLOOKUP(O29,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R29" s="80">
-        <f>IF(P29="","",H29)</f>
-        <v/>
-      </c>
-      <c r="S29" s="82" t="n">
-        <v>67570</v>
-      </c>
-      <c r="T29" s="82" t="n">
-        <v>12073120</v>
-      </c>
-      <c r="U29" s="149" t="n"/>
-      <c r="V29" s="78" t="inlineStr">
-        <is>
-          <t>조운관세사무소</t>
-        </is>
-      </c>
-      <c r="W29" s="82" t="n">
-        <v>286000</v>
-      </c>
-      <c r="X29" s="78" t="inlineStr">
-        <is>
-          <t>진로직스</t>
-        </is>
-      </c>
-      <c r="Y29" s="82" t="n">
-        <v>3909069</v>
-      </c>
-      <c r="Z29" s="82">
-        <f>S29+T29+W29</f>
-        <v/>
-      </c>
-      <c r="AA29" s="83">
-        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE()),0)+Y29+Z29</f>
-        <v/>
-      </c>
-      <c r="AB29" s="84" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC29" s="83">
-        <f>ROUND(AA29/AB29,0)</f>
-        <v/>
-      </c>
-      <c r="AD29" s="78" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="AE29" s="78" t="n"/>
-      <c r="AF29" s="78" t="n"/>
+      <c r="AE29" s="3" t="n"/>
+      <c r="AF29" s="4" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="78" t="n">
@@ -4823,7 +4831,7 @@
       </c>
       <c r="B30" s="78" t="inlineStr">
         <is>
-          <t>CPO696-2</t>
+          <t>CPO696-1</t>
         </is>
       </c>
       <c r="C30" s="78" t="inlineStr">
@@ -4850,7 +4858,7 @@
         </is>
       </c>
       <c r="H30" s="80" t="n">
-        <v>8140</v>
+        <v>78209</v>
       </c>
       <c r="I30" s="150">
         <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
@@ -4873,15 +4881,15 @@
       </c>
       <c r="N30" s="78" t="inlineStr">
         <is>
-          <t>SMC Chiller HRS-040 외</t>
+          <t>CP4445-RGB Projector 외 (렌탈용)</t>
         </is>
       </c>
       <c r="O30" s="149" t="n">
-        <v>46132</v>
+        <v>46129</v>
       </c>
       <c r="P30" s="78" t="inlineStr">
         <is>
-          <t>14008-26-101129M</t>
+          <t>14008-26-101125M</t>
         </is>
       </c>
       <c r="Q30" s="151">
@@ -4893,10 +4901,10 @@
         <v/>
       </c>
       <c r="S30" s="82" t="n">
-        <v>1019820</v>
+        <v>67570</v>
       </c>
       <c r="T30" s="82" t="n">
-        <v>1376760</v>
+        <v>12073120</v>
       </c>
       <c r="U30" s="149" t="n"/>
       <c r="V30" s="78" t="inlineStr">
@@ -4905,7 +4913,7 @@
         </is>
       </c>
       <c r="W30" s="82" t="n">
-        <v>33000</v>
+        <v>286000</v>
       </c>
       <c r="X30" s="78" t="inlineStr">
         <is>
@@ -4913,7 +4921,7 @@
         </is>
       </c>
       <c r="Y30" s="82" t="n">
-        <v>846621</v>
+        <v>3909069</v>
       </c>
       <c r="Z30" s="82">
         <f>S30+T30+W30</f>
@@ -4944,55 +4952,67 @@
       </c>
       <c r="B31" s="78" t="inlineStr">
         <is>
-          <t>EPO18</t>
+          <t>CPO696-2</t>
         </is>
       </c>
       <c r="C31" s="78" t="inlineStr">
         <is>
-          <t>MAICO Italia</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D31" s="78" t="inlineStr">
         <is>
-          <t>100% TT in advance</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E31" s="78" t="inlineStr">
         <is>
-          <t>부품</t>
+          <t>장비</t>
         </is>
       </c>
       <c r="F31" s="149" t="n">
+        <v>46113</v>
+      </c>
+      <c r="G31" s="149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="80" t="n">
+        <v>8140</v>
+      </c>
+      <c r="I31" s="150">
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J31" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="82">
+        <f>IFERROR(ROUND(H31*I31,0),0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="82">
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="82">
+        <f>IFERROR(VLOOKUP(B31,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="78" t="inlineStr">
+        <is>
+          <t>SMC Chiller HRS-040 외</t>
+        </is>
+      </c>
+      <c r="O31" s="149" t="n">
         <v>46132</v>
       </c>
-      <c r="G31" s="149" t="n">
-        <v>46134</v>
-      </c>
-      <c r="H31" s="80" t="n">
-        <v>4388.4</v>
-      </c>
-      <c r="I31" s="150" t="n">
-        <v>1741.08</v>
-      </c>
-      <c r="J31" s="82" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="K31" s="82" t="n">
-        <v>7702082</v>
-      </c>
-      <c r="L31" s="82" t="n">
-        <v>10000</v>
-      </c>
-      <c r="M31" s="82" t="n">
-        <v>8000</v>
-      </c>
-      <c r="N31" s="78" t="inlineStr">
-        <is>
-          <t>AXC 200 ELICENT VENTILATORE/FAN (60EA, EUR)</t>
-        </is>
-      </c>
-      <c r="O31" s="149" t="n"/>
-      <c r="P31" s="78" t="n"/>
+      <c r="P31" s="78" t="inlineStr">
+        <is>
+          <t>14008-26-101129M</t>
+        </is>
+      </c>
       <c r="Q31" s="151">
         <f>IF(P31="","",IFERROR(VLOOKUP(O31,FxRateTable,4,TRUE),""))</f>
         <v/>
@@ -5002,175 +5022,153 @@
         <v/>
       </c>
       <c r="S31" s="82" t="n">
-        <v>0</v>
+        <v>1019820</v>
       </c>
       <c r="T31" s="82" t="n">
-        <v>0</v>
+        <v>1376760</v>
       </c>
       <c r="U31" s="149" t="n"/>
       <c r="V31" s="78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>조운관세사무소</t>
         </is>
       </c>
       <c r="W31" s="82" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="X31" s="78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>진로직스</t>
         </is>
       </c>
       <c r="Y31" s="82" t="n">
-        <v>0</v>
+        <v>846621</v>
       </c>
       <c r="Z31" s="82">
         <f>S31+T31+W31</f>
         <v/>
       </c>
-      <c r="AA31" s="83" t="n">
-        <v>7763609</v>
+      <c r="AA31" s="83">
+        <f>K31+L31+M31+IFERROR(VLOOKUP(B31,RemitTable2,9,FALSE()),0)+Y31+Z31</f>
+        <v/>
       </c>
       <c r="AB31" s="84" t="n">
-        <v>60</v>
-      </c>
-      <c r="AC31" s="83" t="n">
-        <v>129393</v>
-      </c>
-      <c r="AD31" s="78" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AC31" s="83">
+        <f>ROUND(AA31/AB31,0)</f>
+        <v/>
+      </c>
+      <c r="AD31" s="78" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
       <c r="AE31" s="78" t="n"/>
       <c r="AF31" s="78" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="20" t="n">
+      <c r="A32" s="78" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>CPO667</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F32" s="152" t="n">
-        <v>45925</v>
-      </c>
-      <c r="G32" s="153" t="n">
-        <v>46080</v>
-      </c>
-      <c r="H32" s="24" t="n">
-        <v>5673</v>
-      </c>
-      <c r="I32" s="154">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J32" s="26" t="n">
-        <v>205028994</v>
-      </c>
-      <c r="K32" s="26">
-        <f>IFERROR(ROUND(H29*I29,0),0)</f>
-        <v/>
-      </c>
-      <c r="L32" s="26">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M32" s="26">
-        <f>IFERROR(VLOOKUP(B29,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N32" s="20" t="inlineStr">
-        <is>
-          <t>EW CP2220</t>
-        </is>
-      </c>
-      <c r="O32" s="20" t="inlineStr">
+      <c r="B32" s="78" t="inlineStr">
+        <is>
+          <t>EPO18</t>
+        </is>
+      </c>
+      <c r="C32" s="78" t="inlineStr">
+        <is>
+          <t>MAICO Italia</t>
+        </is>
+      </c>
+      <c r="D32" s="78" t="inlineStr">
+        <is>
+          <t>100% TT in advance</t>
+        </is>
+      </c>
+      <c r="E32" s="78" t="inlineStr">
+        <is>
+          <t>부품</t>
+        </is>
+      </c>
+      <c r="F32" s="149" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G32" s="149" t="n">
+        <v>46134</v>
+      </c>
+      <c r="H32" s="80" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="I32" s="150" t="n">
+        <v>1741.08</v>
+      </c>
+      <c r="J32" s="82" t="n">
+        <v>7702082</v>
+      </c>
+      <c r="K32" s="82" t="n">
+        <v>7702082</v>
+      </c>
+      <c r="L32" s="82" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M32" s="82" t="n">
+        <v>8000</v>
+      </c>
+      <c r="N32" s="78" t="inlineStr">
+        <is>
+          <t>AXC 200 ELICENT VENTILATORE/FAN (60EA, EUR)</t>
+        </is>
+      </c>
+      <c r="O32" s="149" t="n"/>
+      <c r="P32" s="78" t="n"/>
+      <c r="Q32" s="151">
+        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R32" s="80">
+        <f>IF(P32="","",H32)</f>
+        <v/>
+      </c>
+      <c r="S32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="149" t="n"/>
+      <c r="V32" s="78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P32" s="20" t="inlineStr">
+      <c r="W32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q32" s="26">
-        <f>IF(P32="","",IFERROR(VLOOKUP(O32,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R32" s="26">
-        <f>IF(P29="","",H29)</f>
-        <v/>
-      </c>
-      <c r="S32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="26">
-        <f>S29+T29+W29</f>
-        <v/>
-      </c>
-      <c r="AA32" s="26">
-        <f>K29+L29+M29+IFERROR(VLOOKUP(B29,RemitTable2,9,FALSE()),0)+Y29+Z29</f>
-        <v/>
-      </c>
-      <c r="AB32" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="26">
-        <f>ROUND(AA29/AB29,0)</f>
-        <v/>
-      </c>
-      <c r="AD32" s="20" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="AE32" s="153" t="inlineStr">
-        <is>
-          <t>2025-09-13</t>
-        </is>
-      </c>
-      <c r="AF32" s="152" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
+      <c r="Y32" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="82">
+        <f>S32+T32+W32</f>
+        <v/>
+      </c>
+      <c r="AA32" s="83" t="n">
+        <v>7763609</v>
+      </c>
+      <c r="AB32" s="84" t="n">
+        <v>60</v>
+      </c>
+      <c r="AC32" s="83" t="n">
+        <v>129393</v>
+      </c>
+      <c r="AD32" s="78" t="n"/>
+      <c r="AE32" s="78" t="n"/>
+      <c r="AF32" s="78" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="20" t="n">
@@ -5178,39 +5176,39 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>GPO458</t>
+          <t>CPO667</t>
         </is>
       </c>
       <c r="C33" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F33" s="152" t="n">
-        <v>45982</v>
+        <v>45925</v>
       </c>
       <c r="G33" s="153" t="n">
-        <v>46020</v>
+        <v>46080</v>
       </c>
       <c r="H33" s="24" t="n">
-        <v>350</v>
+        <v>5673</v>
       </c>
       <c r="I33" s="154">
         <f>IFERROR(VLOOKUP(B30,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J33" s="26" t="n">
-        <v>18264679</v>
+        <v>205028994</v>
       </c>
       <c r="K33" s="26">
         <f>IFERROR(ROUND(H30*I30,0),0)</f>
@@ -5226,7 +5224,7 @@
       </c>
       <c r="N33" s="20" t="inlineStr">
         <is>
-          <t>HFR License</t>
+          <t>EW CP2220</t>
         </is>
       </c>
       <c r="O33" s="20" t="inlineStr">
@@ -5289,17 +5287,17 @@
       </c>
       <c r="AD33" s="20" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2025-09</t>
         </is>
       </c>
       <c r="AE33" s="153" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AF33" s="152" t="inlineStr">
         <is>
-          <t>2026-11-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -5309,39 +5307,39 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>CPO681</t>
+          <t>GPO458</t>
         </is>
       </c>
       <c r="C34" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F34" s="152" t="n">
-        <v>45993</v>
+        <v>45982</v>
       </c>
       <c r="G34" s="153" t="n">
-        <v>46064</v>
+        <v>46020</v>
       </c>
       <c r="H34" s="24" t="n">
-        <v>26358</v>
+        <v>350</v>
       </c>
       <c r="I34" s="154">
         <f>IFERROR(VLOOKUP(B31,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J34" s="26" t="n">
-        <v>38550844</v>
+        <v>18264679</v>
       </c>
       <c r="K34" s="26">
         <f>IFERROR(ROUND(H31*I31,0),0)</f>
@@ -5357,7 +5355,7 @@
       </c>
       <c r="N34" s="20" t="inlineStr">
         <is>
-          <t>EW CP2309/2315/2320-RGB</t>
+          <t>HFR License</t>
         </is>
       </c>
       <c r="O34" s="20" t="inlineStr">
@@ -5425,12 +5423,12 @@
       </c>
       <c r="AE34" s="153" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AF34" s="152" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-11-30</t>
         </is>
       </c>
     </row>
@@ -5440,17 +5438,17 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>GPO459</t>
+          <t>CPO681</t>
         </is>
       </c>
       <c r="C35" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -5459,20 +5457,20 @@
         </is>
       </c>
       <c r="F35" s="152" t="n">
-        <v>46007</v>
+        <v>45993</v>
       </c>
       <c r="G35" s="153" t="n">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="H35" s="24" t="n">
-        <v>450</v>
+        <v>26358</v>
       </c>
       <c r="I35" s="154">
         <f>IFERROR(VLOOKUP(B32,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J35" s="26" t="n">
-        <v>5505104</v>
+        <v>38550844</v>
       </c>
       <c r="K35" s="26">
         <f>IFERROR(ROUND(H32*I32,0),0)</f>
@@ -5488,7 +5486,7 @@
       </c>
       <c r="N35" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 EW</t>
+          <t>EW CP2309/2315/2320-RGB</t>
         </is>
       </c>
       <c r="O35" s="20" t="inlineStr">
@@ -5551,17 +5549,17 @@
       </c>
       <c r="AD35" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="AE35" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="AF35" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-12-21</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5569,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>GPO461</t>
+          <t>GPO459</t>
         </is>
       </c>
       <c r="C36" s="21" t="inlineStr">
@@ -5596,7 +5594,7 @@
         <v>46043</v>
       </c>
       <c r="H36" s="24" t="n">
-        <v>540</v>
+        <v>450</v>
       </c>
       <c r="I36" s="154">
         <f>IFERROR(VLOOKUP(B33,RemitTable2,7,FALSE()),0)</f>
@@ -5619,7 +5617,7 @@
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 EW</t>
+          <t>TMS-2000 EW</t>
         </is>
       </c>
       <c r="O36" s="20" t="inlineStr">
@@ -5682,17 +5680,17 @@
       </c>
       <c r="AD36" s="20" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE36" s="153" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF36" s="152" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -5702,17 +5700,17 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>CPO685</t>
+          <t>GPO461</t>
         </is>
       </c>
       <c r="C37" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -5721,20 +5719,20 @@
         </is>
       </c>
       <c r="F37" s="152" t="n">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="G37" s="153" t="n">
-        <v>46080</v>
+        <v>46043</v>
       </c>
       <c r="H37" s="24" t="n">
-        <v>136516</v>
+        <v>540</v>
       </c>
       <c r="I37" s="154">
         <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J37" s="26" t="n">
-        <v>205028994</v>
+        <v>5505104</v>
       </c>
       <c r="K37" s="26">
         <f>IFERROR(ROUND(H34*I34,0),0)</f>
@@ -5750,7 +5748,7 @@
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (CP2208~CP4450)</t>
+          <t>TMS-1000 EW</t>
         </is>
       </c>
       <c r="O37" s="20" t="inlineStr">
@@ -5813,17 +5811,17 @@
       </c>
       <c r="AD37" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="AE37" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="AF37" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5833,17 +5831,17 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>GPO465</t>
+          <t>CPO685</t>
         </is>
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -5852,22 +5850,20 @@
         </is>
       </c>
       <c r="F38" s="152" t="n">
-        <v>46015</v>
-      </c>
-      <c r="G38" s="153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>46010</v>
+      </c>
+      <c r="G38" s="153" t="n">
+        <v>46080</v>
       </c>
       <c r="H38" s="24" t="n">
-        <v>76054</v>
+        <v>136516</v>
       </c>
       <c r="I38" s="154">
         <f>IFERROR(VLOOKUP(B35,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J38" s="26" t="n">
-        <v>0</v>
+        <v>205028994</v>
       </c>
       <c r="K38" s="26">
         <f>IFERROR(ROUND(H35*I35,0),0)</f>
@@ -5883,7 +5879,7 @@
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>EW 대량 (SR/SX/TMS)</t>
+          <t>EW 대량 (CP2208~CP4450)</t>
         </is>
       </c>
       <c r="O38" s="20" t="inlineStr">
@@ -5966,17 +5962,17 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>CPO686</t>
+          <t>GPO465</t>
         </is>
       </c>
       <c r="C39" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -5985,20 +5981,22 @@
         </is>
       </c>
       <c r="F39" s="152" t="n">
-        <v>46029</v>
-      </c>
-      <c r="G39" s="153" t="n">
-        <v>46072</v>
+        <v>46015</v>
+      </c>
+      <c r="G39" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H39" s="24" t="n">
-        <v>14793</v>
+        <v>76054</v>
       </c>
       <c r="I39" s="154">
         <f>IFERROR(VLOOKUP(B36,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J39" s="26" t="n">
-        <v>25506948</v>
+        <v>0</v>
       </c>
       <c r="K39" s="26">
         <f>IFERROR(ROUND(H36*I36,0),0)</f>
@@ -6014,7 +6012,7 @@
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>EW CP2315/CP4440-RGB</t>
+          <t>EW 대량 (SR/SX/TMS)</t>
         </is>
       </c>
       <c r="O39" s="20" t="inlineStr">
@@ -6082,12 +6080,12 @@
       </c>
       <c r="AE39" s="153" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF39" s="152" t="inlineStr">
         <is>
-          <t>2027-01-29</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6095,7 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>CPO687</t>
+          <t>CPO686</t>
         </is>
       </c>
       <c r="C40" s="21" t="inlineStr">
@@ -6118,20 +6116,18 @@
       <c r="F40" s="152" t="n">
         <v>46029</v>
       </c>
-      <c r="G40" s="153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G40" s="153" t="n">
+        <v>46072</v>
       </c>
       <c r="H40" s="24" t="n">
-        <v>26656</v>
+        <v>14793</v>
       </c>
       <c r="I40" s="154">
         <f>IFERROR(VLOOKUP(B37,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J40" s="26" t="n">
-        <v>0</v>
+        <v>25506948</v>
       </c>
       <c r="K40" s="26">
         <f>IFERROR(ROUND(H37*I37,0),0)</f>
@@ -6147,7 +6143,7 @@
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>EW (홀딩)</t>
+          <t>EW CP2315/CP4440-RGB</t>
         </is>
       </c>
       <c r="O40" s="20" t="inlineStr">
@@ -6215,12 +6211,12 @@
       </c>
       <c r="AE40" s="153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AF40" s="152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-01-29</t>
         </is>
       </c>
     </row>
@@ -6230,39 +6226,41 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>GPO462</t>
+          <t>CPO687</t>
         </is>
       </c>
       <c r="C41" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F41" s="152" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G41" s="153" t="n">
-        <v>46057</v>
+        <v>46029</v>
+      </c>
+      <c r="G41" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H41" s="24" t="n">
-        <v>1440</v>
+        <v>26656</v>
       </c>
       <c r="I41" s="154">
         <f>IFERROR(VLOOKUP(B38,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J41" s="26" t="n">
-        <v>16908206</v>
+        <v>0</v>
       </c>
       <c r="K41" s="26">
         <f>IFERROR(ROUND(H38*I38,0),0)</f>
@@ -6278,7 +6276,7 @@
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>TMS-2000 License</t>
+          <t>EW (홀딩)</t>
         </is>
       </c>
       <c r="O41" s="20" t="inlineStr">
@@ -6346,12 +6344,12 @@
       </c>
       <c r="AE41" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AF41" s="152" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6359,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>GPO463</t>
+          <t>GPO462</t>
         </is>
       </c>
       <c r="C42" s="21" t="inlineStr">
@@ -6376,7 +6374,7 @@
       </c>
       <c r="E42" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F42" s="152" t="n">
@@ -6386,7 +6384,7 @@
         <v>46057</v>
       </c>
       <c r="H42" s="24" t="n">
-        <v>4489</v>
+        <v>1440</v>
       </c>
       <c r="I42" s="154">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE()),0)</f>
@@ -6409,7 +6407,7 @@
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>SX/SR EW (CGV/Lotte)</t>
+          <t>TMS-2000 License</t>
         </is>
       </c>
       <c r="O42" s="20" t="inlineStr">
@@ -6492,7 +6490,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>GPO464</t>
+          <t>GPO463</t>
         </is>
       </c>
       <c r="C43" s="21" t="inlineStr">
@@ -6517,7 +6515,7 @@
         <v>46057</v>
       </c>
       <c r="H43" s="24" t="n">
-        <v>5670.57</v>
+        <v>4489</v>
       </c>
       <c r="I43" s="154">
         <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE()),0)</f>
@@ -6540,7 +6538,7 @@
       </c>
       <c r="N43" s="20" t="inlineStr">
         <is>
-          <t>SR-1000/SX-3000 EW</t>
+          <t>SX/SR EW (CGV/Lotte)</t>
         </is>
       </c>
       <c r="O43" s="20" t="inlineStr">
@@ -6623,17 +6621,17 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>CPO691</t>
+          <t>GPO464</t>
         </is>
       </c>
       <c r="C44" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E44" s="21" t="inlineStr">
@@ -6642,20 +6640,20 @@
         </is>
       </c>
       <c r="F44" s="152" t="n">
+        <v>46042</v>
+      </c>
+      <c r="G44" s="153" t="n">
         <v>46057</v>
       </c>
-      <c r="G44" s="153" t="n">
-        <v>46113</v>
-      </c>
       <c r="H44" s="24" t="n">
-        <v>24614</v>
+        <v>5670.57</v>
       </c>
       <c r="I44" s="154">
         <f>IFERROR(VLOOKUP(B41,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J44" s="26" t="n">
-        <v>51777431</v>
+        <v>16908206</v>
       </c>
       <c r="K44" s="26">
         <f>IFERROR(ROUND(H41*I41,0),0)</f>
@@ -6671,7 +6669,7 @@
       </c>
       <c r="N44" s="20" t="inlineStr">
         <is>
-          <t>EW (메가박스 외)</t>
+          <t>SR-1000/SX-3000 EW</t>
         </is>
       </c>
       <c r="O44" s="20" t="inlineStr">
@@ -6734,17 +6732,17 @@
       </c>
       <c r="AD44" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE44" s="153" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF44" s="152" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-12-31</t>
         </is>
       </c>
     </row>
@@ -6754,17 +6752,17 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>GPO469</t>
+          <t>CPO691</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Net 30 days</t>
+          <t>Net 45 days</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
@@ -6773,20 +6771,20 @@
         </is>
       </c>
       <c r="F45" s="152" t="n">
-        <v>46060</v>
+        <v>46057</v>
       </c>
       <c r="G45" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H45" s="24" t="n">
-        <v>3993.05</v>
+        <v>24614</v>
       </c>
       <c r="I45" s="154">
         <f>IFERROR(VLOOKUP(B42,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J45" s="26" t="n">
-        <v>9919642</v>
+        <v>51777431</v>
       </c>
       <c r="K45" s="26">
         <f>IFERROR(ROUND(H42*I42,0),0)</f>
@@ -6802,7 +6800,7 @@
       </c>
       <c r="N45" s="20" t="inlineStr">
         <is>
-          <t>SR/SX EW (하남미사 외)</t>
+          <t>EW (메가박스 외)</t>
         </is>
       </c>
       <c r="O45" s="20" t="inlineStr">
@@ -6865,17 +6863,17 @@
       </c>
       <c r="AD45" s="20" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="AE45" s="153" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AF45" s="152" t="inlineStr">
         <is>
-          <t>2027-02-22</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
@@ -6885,7 +6883,7 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>GPO470</t>
+          <t>GPO469</t>
         </is>
       </c>
       <c r="C46" s="21" t="inlineStr">
@@ -6900,17 +6898,17 @@
       </c>
       <c r="E46" s="21" t="inlineStr">
         <is>
-          <t>라이센스</t>
+          <t>워런티(EW)</t>
         </is>
       </c>
       <c r="F46" s="152" t="n">
-        <v>46080</v>
+        <v>46060</v>
       </c>
       <c r="G46" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H46" s="24" t="n">
-        <v>360</v>
+        <v>3993.05</v>
       </c>
       <c r="I46" s="154">
         <f>IFERROR(VLOOKUP(B43,RemitTable2,7,FALSE()),0)</f>
@@ -6933,7 +6931,7 @@
       </c>
       <c r="N46" s="20" t="inlineStr">
         <is>
-          <t>TMS-1000 License</t>
+          <t>SR/SX EW (하남미사 외)</t>
         </is>
       </c>
       <c r="O46" s="20" t="inlineStr">
@@ -6996,17 +6994,17 @@
       </c>
       <c r="AD46" s="20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="AE46" s="153" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AF46" s="152" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2027-02-22</t>
         </is>
       </c>
     </row>
@@ -7016,7 +7014,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>GPO471</t>
+          <t>GPO470</t>
         </is>
       </c>
       <c r="C47" s="21" t="inlineStr">
@@ -7035,13 +7033,13 @@
         </is>
       </c>
       <c r="F47" s="152" t="n">
-        <v>46088</v>
+        <v>46080</v>
       </c>
       <c r="G47" s="153" t="n">
         <v>46113</v>
       </c>
       <c r="H47" s="24" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="I47" s="154">
         <f>IFERROR(VLOOKUP(B44,RemitTable2,7,FALSE()),0)</f>
@@ -7064,7 +7062,7 @@
       </c>
       <c r="N47" s="20" t="inlineStr">
         <is>
-          <t>Dolby Atmos License</t>
+          <t>TMS-1000 License</t>
         </is>
       </c>
       <c r="O47" s="20" t="inlineStr">
@@ -7132,12 +7130,12 @@
       </c>
       <c r="AE47" s="153" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="AF47" s="152" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2027-02-28</t>
         </is>
       </c>
     </row>
@@ -7147,55 +7145,55 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>CPO694</t>
+          <t>GPO471</t>
         </is>
       </c>
       <c r="C48" s="21" t="inlineStr">
         <is>
-          <t>Christie</t>
+          <t>GDC</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Net 45 days</t>
+          <t>Net 30 days</t>
         </is>
       </c>
       <c r="E48" s="21" t="inlineStr">
         <is>
-          <t>워런티(EW)</t>
+          <t>라이센스</t>
         </is>
       </c>
       <c r="F48" s="152" t="n">
-        <v>46109</v>
+        <v>46088</v>
       </c>
       <c r="G48" s="153" t="n">
-        <v>46146</v>
+        <v>46113</v>
       </c>
       <c r="H48" s="24" t="n">
-        <v>17404</v>
+        <v>500</v>
       </c>
       <c r="I48" s="154">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,7,FALSE()),0)</f>
         <v/>
       </c>
       <c r="J48" s="26" t="n">
-        <v>0</v>
+        <v>9919642</v>
       </c>
       <c r="K48" s="26">
-        <f>IFERROR(ROUND(H48*I48,0),0)</f>
+        <f>IFERROR(ROUND(H45*I45,0),0)</f>
         <v/>
       </c>
       <c r="L48" s="26">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,10,FALSE()),0)</f>
         <v/>
       </c>
       <c r="M48" s="26">
-        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE()),0)</f>
+        <f>IFERROR(VLOOKUP(B45,RemitTable2,11,FALSE()),0)</f>
         <v/>
       </c>
       <c r="N48" s="20" t="inlineStr">
         <is>
-          <t>EW (CGV 동백 외)</t>
+          <t>Dolby Atmos License</t>
         </is>
       </c>
       <c r="O48" s="20" t="inlineStr">
@@ -7213,7 +7211,7 @@
         <v/>
       </c>
       <c r="R48" s="26">
-        <f>IF(P48="","",H48)</f>
+        <f>IF(P45="","",H45)</f>
         <v/>
       </c>
       <c r="S48" s="26" t="n">
@@ -7242,158 +7240,166 @@
         <v>0</v>
       </c>
       <c r="Z48" s="26">
-        <f>S48+T48+W48</f>
+        <f>S45+T45+W45</f>
         <v/>
       </c>
       <c r="AA48" s="26">
-        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE()),0)+Y48+Z48</f>
+        <f>K45+L45+M45+IFERROR(VLOOKUP(B45,RemitTable2,9,FALSE()),0)+Y45+Z45</f>
         <v/>
       </c>
       <c r="AB48" s="27" t="n">
         <v>1</v>
       </c>
       <c r="AC48" s="26">
-        <f>ROUND(AA48/AB48,0)</f>
+        <f>ROUND(AA45/AB45,0)</f>
         <v/>
       </c>
       <c r="AD48" s="20" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="AE48" s="153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF48" s="152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>CPO694</t>
+        </is>
+      </c>
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F49" s="152" t="n">
+        <v>46109</v>
+      </c>
+      <c r="G49" s="153" t="n">
+        <v>46146</v>
+      </c>
+      <c r="H49" s="24" t="n">
+        <v>17404</v>
+      </c>
+      <c r="I49" s="154">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="26">
+        <f>IFERROR(ROUND(H49*I49,0),0)</f>
+        <v/>
+      </c>
+      <c r="L49" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="26">
+        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>EW (CGV 동백 외)</t>
+        </is>
+      </c>
+      <c r="O49" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P49" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q49" s="26">
+        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R49" s="26">
+        <f>IF(P49="","",H49)</f>
+        <v/>
+      </c>
+      <c r="S49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="26">
+        <f>S49+T49+W49</f>
+        <v/>
+      </c>
+      <c r="AA49" s="26">
+        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
+        <v/>
+      </c>
+      <c r="AB49" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="26">
+        <f>ROUND(AA49/AB49,0)</f>
+        <v/>
+      </c>
+      <c r="AD49" s="20" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE48" s="153" t="inlineStr">
+      <c r="AE49" s="153" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="AF48" s="152" t="inlineStr">
+      <c r="AF49" s="152" t="inlineStr">
         <is>
           <t>2027-03-31</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="85" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="85" t="inlineStr">
-        <is>
-          <t>CPO697</t>
-        </is>
-      </c>
-      <c r="C49" s="85" t="inlineStr">
-        <is>
-          <t>Christie</t>
-        </is>
-      </c>
-      <c r="D49" s="85" t="inlineStr">
-        <is>
-          <t>Net 45 days</t>
-        </is>
-      </c>
-      <c r="E49" s="85" t="inlineStr">
-        <is>
-          <t>워런티(EW)</t>
-        </is>
-      </c>
-      <c r="F49" s="155" t="n">
-        <v>46136</v>
-      </c>
-      <c r="G49" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="87" t="n">
-        <v>15289</v>
-      </c>
-      <c r="I49" s="156">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="89">
-        <f>IFERROR(ROUND(H49*I49,0),0)</f>
-        <v/>
-      </c>
-      <c r="L49" s="89">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="89">
-        <f>IFERROR(VLOOKUP(B49,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N49" s="85" t="inlineStr">
-        <is>
-          <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
-        </is>
-      </c>
-      <c r="O49" s="155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q49" s="157">
-        <f>IF(P49="","",IFERROR(VLOOKUP(O49,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R49" s="87">
-        <f>IF(P49="","",H49)</f>
-        <v/>
-      </c>
-      <c r="S49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="155" t="n"/>
-      <c r="V49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y49" s="89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="89">
-        <f>S49+T49+W49</f>
-        <v/>
-      </c>
-      <c r="AA49" s="89">
-        <f>K49+L49+M49+IFERROR(VLOOKUP(B49,RemitTable2,9,FALSE()),0)+Y49+Z49</f>
-        <v/>
-      </c>
-      <c r="AB49" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" s="89">
-        <f>ROUND(AA49/AB49,0)</f>
-        <v/>
-      </c>
-      <c r="AD49" s="85" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="AE49" s="155" t="n"/>
-      <c r="AF49" s="155" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="85" t="n">
@@ -7401,7 +7407,7 @@
       </c>
       <c r="B50" s="85" t="inlineStr">
         <is>
-          <t>CPO693-2</t>
+          <t>CPO697</t>
         </is>
       </c>
       <c r="C50" s="85" t="inlineStr">
@@ -7420,7 +7426,7 @@
         </is>
       </c>
       <c r="F50" s="155" t="n">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="G50" s="155" t="inlineStr">
         <is>
@@ -7428,7 +7434,7 @@
         </is>
       </c>
       <c r="H50" s="87" t="n">
-        <v>2550</v>
+        <v>15289</v>
       </c>
       <c r="I50" s="156">
         <f>IFERROR(VLOOKUP(B50,RemitTable2,7,FALSE()),0)</f>
@@ -7451,7 +7457,7 @@
       </c>
       <c r="N50" s="85" t="inlineStr">
         <is>
-          <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
+          <t>EW CP4425/CP2308/CP2315/CP2309/CP2320 13대 (메가박스 북대구 외)</t>
         </is>
       </c>
       <c r="O50" s="155" t="inlineStr">
@@ -7519,137 +7525,127 @@
       <c r="AF50" s="155" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="12" t="n">
+      <c r="A51" s="85" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="12" t="inlineStr">
-        <is>
-          <t>CPO688</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="B51" s="85" t="inlineStr">
+        <is>
+          <t>CPO693-2</t>
+        </is>
+      </c>
+      <c r="C51" s="85" t="inlineStr">
         <is>
           <t>Christie</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D51" s="85" t="inlineStr">
         <is>
           <t>Net 45 days</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-      <c r="F51" s="146" t="n">
-        <v>46037</v>
-      </c>
-      <c r="G51" s="147" t="inlineStr">
+      <c r="E51" s="85" t="inlineStr">
+        <is>
+          <t>워런티(EW)</t>
+        </is>
+      </c>
+      <c r="F51" s="155" t="n">
+        <v>46133</v>
+      </c>
+      <c r="G51" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="16" t="n">
-        <v>4180</v>
-      </c>
-      <c r="I51" s="148">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="18">
-        <f>IFERROR(ROUND(H46*I46,0),0)</f>
-        <v/>
-      </c>
-      <c r="L51" s="18">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="18">
-        <f>IFERROR(VLOOKUP(B46,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>Inspection fee</t>
-        </is>
-      </c>
-      <c r="O51" s="12" t="inlineStr">
+      <c r="H51" s="87" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I51" s="156">
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="89">
+        <f>IFERROR(ROUND(H51*I51,0),0)</f>
+        <v/>
+      </c>
+      <c r="L51" s="89">
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M51" s="89">
+        <f>IFERROR(VLOOKUP(B51,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N51" s="85" t="inlineStr">
+        <is>
+          <t>CP4420-RGB 2년 워런티 (CGV 구미)</t>
+        </is>
+      </c>
+      <c r="O51" s="155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P51" s="12" t="inlineStr">
+      <c r="P51" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q51" s="18">
+      <c r="Q51" s="157">
         <f>IF(P51="","",IFERROR(VLOOKUP(O51,FxRateTable,4,TRUE),""))</f>
         <v/>
       </c>
-      <c r="R51" s="18">
-        <f>IF(P46="","",H46)</f>
-        <v/>
-      </c>
-      <c r="S51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="12" t="inlineStr">
+      <c r="R51" s="87">
+        <f>IF(P51="","",H51)</f>
+        <v/>
+      </c>
+      <c r="S51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="155" t="n"/>
+      <c r="V51" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="W51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="13" t="inlineStr">
+      <c r="W51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y51" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="18">
-        <f>S46+T46+W46</f>
-        <v/>
-      </c>
-      <c r="AA51" s="18">
-        <f>K46+L46+M46+IFERROR(VLOOKUP(B46,RemitTable2,9,FALSE()),0)+Y46+Z46</f>
-        <v/>
-      </c>
-      <c r="AB51" s="19" t="n">
+      <c r="Y51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="89">
+        <f>S51+T51+W51</f>
+        <v/>
+      </c>
+      <c r="AA51" s="89">
+        <f>K51+L51+M51+IFERROR(VLOOKUP(B51,RemitTable2,9,FALSE()),0)+Y51+Z51</f>
+        <v/>
+      </c>
+      <c r="AB51" s="90" t="n">
         <v>1</v>
       </c>
-      <c r="AC51" s="18">
-        <f>ROUND(AA46/AB46,0)</f>
-        <v/>
-      </c>
-      <c r="AD51" s="12" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="AE51" s="147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF51" s="146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AC51" s="89">
+        <f>ROUND(AA51/AB51,0)</f>
+        <v/>
+      </c>
+      <c r="AD51" s="85" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="AE51" s="155" t="n"/>
+      <c r="AF51" s="155" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="12" t="n">
@@ -7657,28 +7653,34 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>SX3000수리</t>
+          <t>CPO688</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>GDC</t>
+          <t>Christie</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
+          <t>Net 45 days</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>Inspection</t>
+        </is>
+      </c>
+      <c r="F52" s="146" t="n">
+        <v>46037</v>
+      </c>
+      <c r="G52" s="147" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>수리반환</t>
-        </is>
-      </c>
-      <c r="F52" s="146" t="n"/>
-      <c r="G52" s="147" t="n"/>
       <c r="H52" s="16" t="n">
-        <v>400</v>
+        <v>4180</v>
       </c>
       <c r="I52" s="148">
         <f>IFERROR(VLOOKUP(B47,RemitTable2,7,FALSE()),0)</f>
@@ -7701,15 +7703,17 @@
       </c>
       <c r="N52" s="12" t="inlineStr">
         <is>
-          <t>Display Card (수리반환 5PCS)</t>
-        </is>
-      </c>
-      <c r="O52" s="12" t="n">
-        <v>46125</v>
+          <t>Inspection fee</t>
+        </is>
+      </c>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>2235626351613M</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q52" s="18">
@@ -7724,12 +7728,14 @@
         <v>0</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>67750</v>
-      </c>
-      <c r="U52" s="13" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="U52" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="V52" s="12" t="inlineStr">
         <is>
-          <t>운서합동</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W52" s="18" t="n">
@@ -7737,7 +7743,7 @@
       </c>
       <c r="X52" s="13" t="inlineStr">
         <is>
-          <t>DHL</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y52" s="18" t="n">
@@ -7752,7 +7758,7 @@
         <v/>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC52" s="18">
         <f>ROUND(AA47/AB47,0)</f>
@@ -7760,140 +7766,134 @@
       </c>
       <c r="AD52" s="12" t="inlineStr">
         <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="AE52" s="147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF52" s="146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>SX3000수리</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>GDC</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>수리반환</t>
+        </is>
+      </c>
+      <c r="F53" s="146" t="n"/>
+      <c r="G53" s="147" t="n"/>
+      <c r="H53" s="16" t="n">
+        <v>400</v>
+      </c>
+      <c r="I53" s="148">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,7,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="J53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="18">
+        <f>IFERROR(ROUND(H48*I48,0),0)</f>
+        <v/>
+      </c>
+      <c r="L53" s="18">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,10,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="M53" s="18">
+        <f>IFERROR(VLOOKUP(B48,RemitTable2,11,FALSE()),0)</f>
+        <v/>
+      </c>
+      <c r="N53" s="12" t="inlineStr">
+        <is>
+          <t>Display Card (수리반환 5PCS)</t>
+        </is>
+      </c>
+      <c r="O53" s="12" t="n">
+        <v>46125</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>2235626351613M</t>
+        </is>
+      </c>
+      <c r="Q53" s="18">
+        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
+        <v/>
+      </c>
+      <c r="R53" s="18">
+        <f>IF(P48="","",H48)</f>
+        <v/>
+      </c>
+      <c r="S53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="18" t="n">
+        <v>67750</v>
+      </c>
+      <c r="U53" s="13" t="n"/>
+      <c r="V53" s="12" t="inlineStr">
+        <is>
+          <t>운서합동</t>
+        </is>
+      </c>
+      <c r="W53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="13" t="inlineStr">
+        <is>
+          <t>DHL</t>
+        </is>
+      </c>
+      <c r="Y53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="18">
+        <f>S48+T48+W48</f>
+        <v/>
+      </c>
+      <c r="AA53" s="18">
+        <f>K48+L48+M48+IFERROR(VLOOKUP(B48,RemitTable2,9,FALSE()),0)+Y48+Z48</f>
+        <v/>
+      </c>
+      <c r="AB53" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC53" s="18">
+        <f>ROUND(AA48/AB48,0)</f>
+        <v/>
+      </c>
+      <c r="AD53" s="12" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="AE52" s="147" t="n"/>
-      <c r="AF52" s="146" t="n"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>IPO016</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>Integ Process Group</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>50% TT advance, 50% Net 30</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>부품</t>
-        </is>
-      </c>
-      <c r="F53" s="143" t="n">
-        <v>45881</v>
-      </c>
-      <c r="G53" s="144" t="n">
-        <v>46146</v>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>6800</v>
-      </c>
-      <c r="I53" s="145">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,7,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="J53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="9">
-        <f>IFERROR(ROUND(H53*I53,0),0)</f>
-        <v/>
-      </c>
-      <c r="L53" s="9">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,10,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="9">
-        <f>IFERROR(VLOOKUP(B53,RemitTable2,11,FALSE()),0)</f>
-        <v/>
-      </c>
-      <c r="N53" s="3" t="inlineStr">
-        <is>
-          <t>JNIOR Model 410 (20EA)</t>
-        </is>
-      </c>
-      <c r="O53" s="144" t="n">
-        <v>45905</v>
-      </c>
-      <c r="P53" s="3" t="inlineStr">
-        <is>
-          <t>883504210357</t>
-        </is>
-      </c>
-      <c r="Q53" s="7">
-        <f>IF(P53="","",IFERROR(VLOOKUP(O53,FxRateTable,4,TRUE),""))</f>
-        <v/>
-      </c>
-      <c r="R53" s="7">
-        <f>IF(P53="","",H53)</f>
-        <v/>
-      </c>
-      <c r="S53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="9" t="n">
-        <v>954760</v>
-      </c>
-      <c r="U53" s="143" t="n">
-        <v>45905</v>
-      </c>
-      <c r="V53" s="3" t="inlineStr">
-        <is>
-          <t>인천세관</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="4" t="inlineStr">
-        <is>
-          <t>DHL</t>
-        </is>
-      </c>
-      <c r="Y53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="9">
-        <f>S53+T53+W53</f>
-        <v/>
-      </c>
-      <c r="AA53" s="175">
-        <f>K53+L53+M53+IFERROR(VLOOKUP(B53,RemitTable2,9,FALSE()),0)+Y53+Z53</f>
-        <v/>
-      </c>
-      <c r="AB53" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC53" s="175">
-        <f>ROUND(AA53/AB53,0)</f>
-        <v/>
-      </c>
-      <c r="AD53" s="3" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="AE53" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF53" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AE53" s="147" t="n"/>
+      <c r="AF53" s="146" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="125" t="inlineStr">
@@ -7908,24 +7908,24 @@
       <c r="F54" s="126" t="n"/>
       <c r="G54" s="127" t="n"/>
       <c r="H54" s="91">
-        <f>SUBTOTAL(9,H5:H31,H53)</f>
+        <f>SUBTOTAL(9,H5:H32)</f>
         <v/>
       </c>
       <c r="I54" s="92" t="n"/>
       <c r="J54" s="93">
-        <f>SUBTOTAL(9,J5:J31,J53)</f>
+        <f>SUBTOTAL(9,J5:J32)</f>
         <v/>
       </c>
       <c r="K54" s="93">
-        <f>SUBTOTAL(9,K5:K31,K53)</f>
+        <f>SUBTOTAL(9,K5:K32)</f>
         <v/>
       </c>
       <c r="L54" s="93">
-        <f>SUBTOTAL(9,L5:L31,L53)</f>
+        <f>SUBTOTAL(9,L5:L32)</f>
         <v/>
       </c>
       <c r="M54" s="93">
-        <f>SUBTOTAL(9,M5:M28,M53)</f>
+        <f>SUBTOTAL(9,M5:M29)</f>
         <v/>
       </c>
       <c r="N54" s="92" t="n"/>
@@ -7934,30 +7934,30 @@
       <c r="Q54" s="93" t="n"/>
       <c r="R54" s="91" t="n"/>
       <c r="S54" s="93">
-        <f>SUBTOTAL(9,S5:S31,S53)</f>
+        <f>SUBTOTAL(9,S5:S32)</f>
         <v/>
       </c>
       <c r="T54" s="93">
-        <f>SUBTOTAL(9,T5:T31,T53)</f>
+        <f>SUBTOTAL(9,T5:T32)</f>
         <v/>
       </c>
       <c r="U54" s="92" t="n"/>
       <c r="V54" s="92" t="n"/>
       <c r="W54" s="93">
-        <f>SUBTOTAL(9,W5:W31,W53)</f>
+        <f>SUBTOTAL(9,W5:W32)</f>
         <v/>
       </c>
       <c r="X54" s="92" t="n"/>
       <c r="Y54" s="93">
-        <f>SUBTOTAL(9,Y5:Y31,Y53)</f>
+        <f>SUBTOTAL(9,Y5:Y32)</f>
         <v/>
       </c>
       <c r="Z54" s="93">
-        <f>SUBTOTAL(9,Z5:Z31,Z53)</f>
+        <f>SUBTOTAL(9,Z5:Z32)</f>
         <v/>
       </c>
       <c r="AA54" s="93">
-        <f>SUBTOTAL(9,AA5:AA31,AA53)</f>
+        <f>SUBTOTAL(9,AA5:AA32)</f>
         <v/>
       </c>
       <c r="AB54" s="92" t="n"/>
@@ -7979,24 +7979,24 @@
       <c r="F55" s="126" t="n"/>
       <c r="G55" s="127" t="n"/>
       <c r="H55" s="91">
-        <f>SUBTOTAL(9,H32:H50)</f>
+        <f>SUBTOTAL(9,H33:H51)</f>
         <v/>
       </c>
       <c r="I55" s="92" t="n"/>
       <c r="J55" s="93">
-        <f>SUBTOTAL(9,J32:J50)</f>
+        <f>SUBTOTAL(9,J33:J51)</f>
         <v/>
       </c>
       <c r="K55" s="93">
-        <f>SUBTOTAL(9,K32:K50)</f>
+        <f>SUBTOTAL(9,K33:K51)</f>
         <v/>
       </c>
       <c r="L55" s="93">
-        <f>SUBTOTAL(9,L32:L50)</f>
+        <f>SUBTOTAL(9,L33:L51)</f>
         <v/>
       </c>
       <c r="M55" s="93">
-        <f>SUBTOTAL(9,M29:M45)</f>
+        <f>SUBTOTAL(9,M30:M46)</f>
         <v/>
       </c>
       <c r="N55" s="92" t="n"/>
@@ -8005,30 +8005,30 @@
       <c r="Q55" s="93" t="n"/>
       <c r="R55" s="91" t="n"/>
       <c r="S55" s="93">
-        <f>SUBTOTAL(9,S32:S50)</f>
+        <f>SUBTOTAL(9,S33:S51)</f>
         <v/>
       </c>
       <c r="T55" s="93">
-        <f>SUBTOTAL(9,T32:T50)</f>
+        <f>SUBTOTAL(9,T33:T51)</f>
         <v/>
       </c>
       <c r="U55" s="92" t="n"/>
       <c r="V55" s="92" t="n"/>
       <c r="W55" s="93">
-        <f>SUBTOTAL(9,W32:W50)</f>
+        <f>SUBTOTAL(9,W33:W51)</f>
         <v/>
       </c>
       <c r="X55" s="92" t="n"/>
       <c r="Y55" s="93">
-        <f>SUBTOTAL(9,Y32:Y50)</f>
+        <f>SUBTOTAL(9,Y33:Y51)</f>
         <v/>
       </c>
       <c r="Z55" s="93">
-        <f>SUBTOTAL(9,Z32:Z50)</f>
+        <f>SUBTOTAL(9,Z33:Z51)</f>
         <v/>
       </c>
       <c r="AA55" s="93">
-        <f>SUBTOTAL(9,AA32:AA50)</f>
+        <f>SUBTOTAL(9,AA33:AA51)</f>
         <v/>
       </c>
       <c r="AB55" s="92" t="n"/>
@@ -8050,24 +8050,24 @@
       <c r="F56" s="126" t="n"/>
       <c r="G56" s="127" t="n"/>
       <c r="H56" s="91">
-        <f>H51+H52</f>
+        <f>H52+H53</f>
         <v/>
       </c>
       <c r="I56" s="92" t="n"/>
       <c r="J56" s="93">
-        <f>J51+J52</f>
+        <f>J52+J53</f>
         <v/>
       </c>
       <c r="K56" s="93">
-        <f>K51+K52</f>
+        <f>K52+K53</f>
         <v/>
       </c>
       <c r="L56" s="93">
-        <f>L51+L52</f>
+        <f>L52+L53</f>
         <v/>
       </c>
       <c r="M56" s="93">
-        <f>M46+M47</f>
+        <f>M47+M48</f>
         <v/>
       </c>
       <c r="N56" s="92" t="n"/>
@@ -8076,30 +8076,30 @@
       <c r="Q56" s="93" t="n"/>
       <c r="R56" s="91" t="n"/>
       <c r="S56" s="93">
-        <f>S51+S52</f>
+        <f>S52+S53</f>
         <v/>
       </c>
       <c r="T56" s="93">
-        <f>T51+T52</f>
+        <f>T52+T53</f>
         <v/>
       </c>
       <c r="U56" s="92" t="n"/>
       <c r="V56" s="92" t="n"/>
       <c r="W56" s="93">
-        <f>W51+W52</f>
+        <f>W52+W53</f>
         <v/>
       </c>
       <c r="X56" s="92" t="n"/>
       <c r="Y56" s="93">
-        <f>Y51+Y52</f>
+        <f>Y52+Y53</f>
         <v/>
       </c>
       <c r="Z56" s="93">
-        <f>Z51+Z52</f>
+        <f>Z52+Z53</f>
         <v/>
       </c>
       <c r="AA56" s="93">
-        <f>AA51+AA52</f>
+        <f>AA52+AA53</f>
         <v/>
       </c>
       <c r="AB56" s="92" t="n"/>
@@ -8138,7 +8138,7 @@
         <v/>
       </c>
       <c r="M57" s="96">
-        <f>SUBTOTAL(9,M5:M53)</f>
+        <f>SUBTOTAL(9,M5:M48)</f>
         <v/>
       </c>
       <c r="N57" s="95" t="n"/>
